--- a/datasets/AU_attributes/aposteriori_unimodal_attitudes.gender.xlsx
+++ b/datasets/AU_attributes/aposteriori_unimodal_attitudes.gender.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,85 +441,80 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>toany</t>
+          <t>annotatorMinority</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>annotatorMinority</t>
+          <t>annotatorPolitics</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>bert</t>
+          <t>traditionalism</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>annotatorPolitics</t>
+          <t>annotatorRace</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>traditionalism</t>
+          <t>annotatorAge</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>annotatorRace</t>
+          <t>annotatorGender</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>annotatorAge</t>
+          <t>freeSpeech</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>annotatorGender</t>
+          <t>harmHateSpeech</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>freeSpeech</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>harmHateSpeech</t>
+          <t>lingPurism</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>racism</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>lingPurism</t>
+          <t>racist</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>racism</t>
+          <t>annotator_count</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>racist</t>
+          <t>scores</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>scores</t>
+          <t>HIST</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>HIST</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>DFU</t>
         </is>
@@ -541,85 +536,78 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 4, 4, 2]</t>
+          <t>['{}', '{}', 'none', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['{}', '{}', 'none', '{}', '{}', '{}']</t>
+          <t>['left', 'far left', 'left', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[0.2549588084220886, -0.04279607906937599, 0.26560378074645996, -0.3767315745353699, -0.3549652397632599, -0.23256109654903412, 0.4496613144874573, 0.5256175994873047, -0.05654732137918472, -0.26085948944091797, 0.049608562141656876, -0.08607245981693268, -0.3291383385658264, 0.005277577787637711, 0.04002439230680466, 0.4844098687171936, -0.04608556628227234, 0.35683634877204895, -0.02110682986676693, 0.43879666924476624, -0.11068738251924515, -0.3693843185901642, 0.4704199433326721, -0.45801886916160583, -0.050300829112529755, 0.03809237852692604, -0.28168055415153503, -0.07020410150289536, -0.3041747212409973, 0.2970273196697235, -0.07806872576475143, 0.13569945096969604, -0.24482497572898865, -0.5763372778892517, 0.5002734661102295, 0.1062828078866005, -0.033531710505485535, 0.049724284559488297, 0.32522454857826233, 0.22696085274219513, -0.2998397648334503, -0.19504821300506592, 0.29941731691360474, -0.18757036328315735, -0.18528038263320923, -0.6294947862625122, -3.593409776687622, 0.22397173941135406, -0.4258723855018616, -0.5664904713630676, 0.5136809349060059, -0.11249349266290665, -0.30440273880958557, 0.6634542346000671, 0.06688881665468216, 0.49178948998451233, -0.37520352005958557, -0.3624446392059326, -0.12137652188539505, -0.2665611207485199, 0.3352321684360504, 4.9819784180726856e-05, -0.25355857610702515, 0.3126324713230133, 0.014876572415232658, 0.3384377062320709, -0.527080237865448, 0.6090782284736633, -0.3500036299228668, 0.4839012622833252, -0.2802498936653137, 0.0007997317588888109, 0.09470897912979126, -0.28072571754455566, 0.016545994207262993, -0.43382421135902405, -0.28910353779792786, 0.34954848885536194, -0.1747034341096878, -0.04166099429130554, -0.47558534145355225, 0.5564690232276917, 0.3360128104686737, 0.005561418365687132, 0.47342541813850403, 0.5415414571762085, 0.0009404526790603995, -0.23718459904193878, 0.2870502471923828, 0.14602097868919373, 0.23688779771327972, -0.03601040318608284, 0.01210443489253521, 0.4213574528694153, 0.20073293149471283, 0.22934557497501373, 0.24520055949687958, 0.2829878330230713, 0.011905218474566936, 0.11206604540348053, 0.12256474792957306, 0.04766949638724327, 0.35539814829826355, -0.4589287340641022, -0.09431123733520508, -0.3935299813747406, 0.08001132309436798, 0.03786924108862877, 0.07058175653219223, -1.9040940999984741, 0.052859824150800705, 0.017846737056970596, -0.05638284981250763, -0.3912097215652466, -0.005553272552788258, -0.2466040998697281, 0.7368057370185852, 0.03501254692673683, 0.3213043808937073, 0.27556413412094116, -0.6103631854057312, 0.12136857956647873, 0.17693646252155304, -0.22724872827529907, 0.5140447020530701, 0.34600284695625305, 0.01881883479654789, 0.03835831210017204, 0.7003686428070068, 0.4300663471221924, 0.17089004814624786, 0.30288729071617126, -0.24492833018302917, -0.021084100008010864, -0.20335069298744202, -0.22563877701759338, 0.37476351857185364, -0.3121265172958374, 0.015567028895020485, -0.32985013723373413, -0.7320888042449951, -0.4183189868927002, -2.77628231048584, 0.27796226739883423, 0.4420776665210724, 0.0807734876871109, -0.4113875925540924, -0.191524475812912, -0.006899658124893904, 0.5044755339622498, -0.00025326921604573727, -0.1614789515733719, 0.2606201171875, 0.17031820118427277, -0.1964079588651657, -0.05979541316628456, -0.26656872034072876, -0.3036433756351471, -0.2585105895996094, 0.697729766368866, 0.23031042516231537, -0.041228000074625015, -0.07500995695590973, 0.3327782452106476, 0.1781322956085205, -0.10031314939260483, 0.09396570920944214, -0.008569466881453991, -0.2957850992679596, 0.13665029406547546, 0.07142182439565659, -0.46965456008911133, 0.5394201874732971, 0.10262171179056168, 0.3668295741081238, 0.05187525227665901, -0.18466854095458984, 0.2242080271244049, 0.2875024080276489, -0.2155073583126068, -0.39512181282043457, 0.7632268071174622, -0.22838690876960754, 0.2624800205230713, 0.2809161841869354, -0.512539803981781, 0.49377843737602234, -0.09412448853254318, -0.07122517377138138, 0.0020254943519830704, -0.2206009030342102, -0.21057264506816864, 0.4795599579811096, 0.5689777731895447, 0.2250744253396988, -0.3635539412498474, -0.474597692489624, -0.5474570989608765, -0.00781890470534563, -0.048044268041849136, 0.09959662705659866, -0.4036373794078827, 0.21310675144195557, 0.13245388865470886, -0.4361826777458191, 4.149281024932861, 0.22473318874835968, -0.15874658524990082, -0.020808739587664604, 0.6640117168426514, -0.4430791437625885, 0.06735444068908691, -0.12195328623056412, -0.177125483751297, -0.16851463913917542, -0.012445309199392796, 0.42117077112197876, 0.30965742468833923, 0.11465881019830704, 0.09590136259794235, -0.011537211947143078, 0.2530096769332886, -0.3415237069129944, 0.49205848574638367, -0.3061327636241913, 0.5232052803039551, -0.10428912192583084, 0.19209876656532288, 0.5422918796539307, -1.532544493675232, 0.246012344956398, 0.09109044075012207, -0.32110679149627686, 0.176803320646286, -0.05247461423277855, 0.3323676288127899, 0.252079039812088, -0.172410786151886, -0.1480942666530609, -0.4206024408340454, -0.1453336924314499, 0.5987367630004883, -0.08240364491939545, -0.04142671078443527, -0.31033968925476074, 0.0008102594874799252, 0.10055655241012573, -0.9105516672134399, 0.291351854801178, -0.009455081075429916, 0.4487314224243164, 0.29480722546577454, 0.014884984120726585, -0.426008015871048, -0.001282291836105287, 0.16394518315792084, -0.164867103099823, 0.14143046736717224, -0.40633416175842285, -0.6409538984298706, -0.3494032919406891, 0.09068123996257782, -0.21162733435630798, 0.2506096363067627, -0.6097872257232666, -0.37046122550964355, -0.06813903898000717, 0.03303927928209305, -0.11642041057348251, -0.40150564908981323, 0.10333860665559769, -0.05967359617352486, -0.49693503975868225, -2.8783493041992188, 0.13588163256645203, -0.3318274915218353, -0.054455019533634186, 0.11624456197023392, -0.3354329764842987, -0.3810169994831085, 0.7215085029602051, 0.14945626258850098, -0.03207191079854965, 0.2694941759109497, 0.626599907875061, -0.17420649528503418, 0.19652992486953735, 0.1606835573911667, -0.04621585085988045, -0.18704362213611603, -0.7920025587081909, -0.40692245960235596, -0.1963990479707718, 0.18283525109291077, 0.3943916857242584, -0.3779144585132599, 0.16313062608242035, 0.4918605387210846, -0.03316369652748108, -0.2832682728767395, -0.10277265310287476, 0.4238119125366211, -0.43799468874931335, 0.5107025504112244, -0.21078677475452423, -0.3288137912750244, -0.1456412672996521, -0.37799638509750366, -3.7196061611175537, 0.34323519468307495, -0.18865275382995605, -0.5359081625938416, 0.2303491085767746, -0.27829161286354065, 0.4390616714954376, 0.16845320165157318, -0.2763145864009857, -0.171417698264122, 0.07921445369720459, -0.5049089789390564, 0.22146449983119965, -0.29294678568840027, 0.29166534543037415, 0.5925953388214111, 0.5152490139007568, -0.23454047739505768, 0.14624999463558197, 0.12251067161560059, 0.2936651110649109, 0.011450809426605701, -0.1148633360862732, 0.07054267078638077, 0.35938695073127747, 0.46673572063446045, -0.2547539472579956, -0.22479447722434998, 0.06839868426322937, -0.04952471703290939, 0.6103218793869019, 0.03850964456796646, 0.11836523562669754, -0.24441449344158173, -0.43007692694664, -0.02740814909338951, 0.3337510824203491, -0.013529479503631592, 0.04896264895796776, 0.3119787275791168, 0.051930610090494156, 0.37107062339782715, 0.2589932084083557, -0.12478610873222351, 0.6703726649284363, -0.4832932651042938, 0.06464026868343353, -0.28195416927337646, -0.08156237751245499, -0.18481382727622986, -0.34071439504623413, -0.37433817982673645, 0.9797595739364624, -0.05912042036652565, 0.22883300483226776, -0.05886419117450714, 0.22962580621242523, 0.1739923357963562, -0.1368008852005005, 0.12278620153665543, 0.6760831475257874, -0.3652017414569855, 0.15849897265434265, -0.16031406819820404, 0.15031254291534424, -0.28578272461891174, -0.08787397295236588, -0.536974310874939, 0.189457967877388, 0.49318331480026245, 0.06939433515071869, 0.5105836391448975, -0.02040945738554001, -1.3326516151428223, 0.01900695450603962, -0.09663613885641098, -0.45487645268440247, 0.11088865995407104, 0.006074532400816679, 0.31467363238334656, 0.199070543050766, 0.16016066074371338, -0.10768242925405502, 0.545192539691925, -0.5974650382995605, -0.21733282506465912, 0.18136917054653168, 0.44656822085380554, -0.8063190579414368, 0.21000027656555176, -0.23697233200073242, 0.22543291747570038, 0.2749888300895691, 0.14114461839199066, 0.27545297145843506, 0.4151051938533783, 0.5351572036743164, -1.170509934425354, 0.4236030876636505, -0.09338057041168213, 0.5968385934829712, -0.05744592100381851, 0.030408820137381554, -0.295186847448349, -0.2981942594051361, 0.025675756856799126, -0.006825317163020372, 0.1260911226272583, 0.3506764769554138, 0.09261079132556915, 0.19346176087856293, 0.12096301466226578, -0.5578768253326416, 0.34496405720710754, 0.7249370813369751, -0.14705245196819305, -0.38524559140205383, 0.7148582339286804, 0.33781367540359497, -0.19105154275894165, 0.5701912045478821, 0.02174103446304798, -0.2037804126739502, -0.2811163365840912, -0.04631570354104042, 0.06218697130680084, 0.05956215411424637, 0.12243109941482544, -0.3345380127429962, 0.15527310967445374, -0.11269308626651764, -0.2608514428138733, -0.44607818126678467, -0.3105531632900238, -0.1395336091518402, -0.1386214643716812, -0.09692385792732239, 0.33352407813072205, 0.05123809352517128, -0.07588442414999008, 0.6477847099304199, -0.22452262043952942, -0.5022566914558411, 0.47778117656707764, -0.333339124917984, 0.9322429299354553, -0.2536472976207733, -0.14599214494228363, -0.10327409207820892, 0.4413609504699707, -0.18806308507919312, -0.37639233469963074, -0.044304169714450836, -0.41296887397766113, 0.17141200602054596, 0.2777380049228668, -0.006794263143092394, 0.23846861720085144, -0.9033740162849426, -0.14283941686153412, 0.12575019896030426, 0.04161132872104645, -1.741843819618225, 0.03559373319149017, 0.33467692136764526, -0.46227604150772095, 0.44572505354881287, -0.11605580896139145, -0.4066874384880066, 0.5850954055786133, -0.36493271589279175, 0.07563504576683044, -0.350383996963501, -0.09726639837026596, -0.12270306050777435, 0.2627144157886505, 0.4463733732700348, -0.04784489423036575, -0.1904309093952179, -0.516362190246582, -0.36392727494239807, -0.36137959361076355, 0.037988025695085526, 0.49541333317756653, 0.5836870074272156, 0.09430538862943649, 0.12323211133480072, -0.11785263568162918, -0.0036688733380287886, 0.32015252113342285, -0.17997193336486816, 0.036097098141908646, 0.02140960656106472, -0.1554720550775528, -0.45674413442611694, 0.12751302123069763, 0.7873355150222778, 0.8039162755012512, -0.08527366816997528, 0.6625829339027405, 0.8909700512886047, 0.7836833596229553, -0.2577782869338989, -0.19194446504116058, 0.42252787947654724, 0.6453046202659607, 0.5697581171989441, -0.04489200562238693, -0.17101025581359863, 0.18697847425937653, 0.6226036548614502, -0.18881529569625854, -0.26764219999313354, -0.41075122356414795, -0.5471557378768921, -0.5474461913108826, -0.04375725984573364, -0.4213534891605377, 0.10874565690755844, -0.2144143283367157, -0.4446055591106415, -0.010666544549167156, -0.13295413553714752, 0.3907022774219513, -0.42579078674316406, 0.06969273835420609, -0.6022223830223083, -0.5790014266967773, 0.17644642293453217, -0.07384427636861801, -0.08331259340047836, 0.4860802888870239, 0.2516051232814789, 0.5365749597549438, -0.4459613561630249, 0.21638989448547363, -0.06946753710508347, 0.5725817084312439, -0.035814907401800156, -0.10932167619466782, 0.12041881680488586, -0.19910719990730286, 0.38486605882644653, -0.642295777797699, -0.21056890487670898, 0.7123121023178101, -0.15131425857543945, 0.3622967302799225, 0.031242666766047478, -0.09766609966754913, 0.3327103555202484, 0.1470946967601776, -0.7020360827445984, -0.1508057564496994, -0.3043348491191864, 0.2886609137058258, 0.14358662068843842, -0.1578478217124939, -0.08281069993972778, 0.11760526895523071, -0.1696428805589676, -0.019223904237151146, -0.09737465530633926, 0.380831241607666, 0.35467851161956787, -0.14383618533611298, 0.4803646206855774, 0.18595270812511444, 0.4988105297088623, 0.22830897569656372, -0.1391541212797165, -0.35690778493881226, 0.29855582118034363, 0.19859769940376282, -0.4952565133571625, -0.027586739510297775, 0.04444248601794243, -0.43366748094558716, 0.6575703024864197, -0.31570136547088623, 2.0384411811828613, 0.20514768362045288, 0.3229205906391144, -0.06521524488925934, 0.7687573432922363, 0.1483178734779358, 0.16517387330532074, 0.12673194706439972, -0.6971262693405151, 0.5567576289176941, -0.5113340020179749, 0.12760873138904572, -0.2095595747232437, 0.004614305682480335, 0.7216553092002869, 0.5733866095542908, 0.3766668736934662, -0.4398851990699768, -0.4595448076725006, -0.0698273703455925, -0.1762963980436325, 0.05753085017204285, 0.1915564388036728, 0.48794475197792053, -0.35738515853881836, 0.09706516563892365, 0.04642048478126526, -0.3255188465118408, 0.23908694088459015, 0.273532509803772, -0.6910536289215088, -0.12528949975967407, 0.4810825288295746, 0.16848716139793396, 0.018274934962391853, -0.2737099528312683, 0.05419621989130974, -0.16909897327423096, -0.3818407952785492, -0.1724545657634735, 0.18405543267726898, 0.1867639422416687, 0.9108594059944153, -0.013842093758285046, 0.16774366796016693, 0.37111037969589233, -0.2382890284061432, -0.1672319620847702, 0.6279321908950806, 0.36234596371650696, -0.2842925786972046, -0.03659893572330475, -0.42961880564689636, -0.20839823782444, 0.3415548801422119, -0.4764597713947296, 0.2496679127216339, -0.3336617052555084, -0.24522113800048828, 0.3368929922580719, -0.16231338679790497, 0.7582753300666809, 0.6367065906524658, -0.25951388478279114, -0.2548162639141083, 0.22149094939231873, 0.10359492897987366, -0.025226479396224022, 0.4605134129524231, -0.3924718201160431, -0.08508642017841339, 0.5598781704902649, 0.261134535074234, 0.05695568397641182, 0.49804553389549255, 0.3759669363498688, -0.10553660243749619, -0.39296719431877136, -0.5773807168006897, -2.1916608810424805, 0.29708871245384216, 0.24792470037937164, 0.11693427711725235, -0.3608839213848114, 0.3035431504249573, 0.1504390835762024, -0.106804758310318, 0.2572179436683655, -0.35152846574783325, 0.1700812727212906, 0.11676980555057526, 0.25449174642562866, -0.7040947079658508, 0.4106605052947998, -0.4190802574157715, 0.3136593997478485, -0.09036087989807129, -0.08411995321512222, -0.5861411094665527, 0.040499135851860046, 0.07484648376703262, -0.26274117827415466, -0.38518810272216797, -0.4006281793117523, 0.22632382810115814, -0.00830919947475195, -0.09085535258054733, 0.010530957952141762, 0.08180209994316101, -0.09704545885324478, 0.15058866143226624, -0.4726261496543884, -0.3408280313014984, 0.19299447536468506, -0.0734642818570137, -0.231380432844162, 0.34831276535987854, -0.07926657795906067, 0.34630435705184937, 0.08747189491987228, 0.6129181981086731, 0.030199570581316948, 0.11325746029615402, -0.00827007181942463, -0.14151805639266968, 0.3805709779262543, -0.13277769088745117, 0.6232001781463623, -0.0766608789563179, 0.11707402020692825, -0.16699270904064178, 0.36835384368896484, -0.05986787751317024, 0.1276583969593048, 0.24864383041858673, 0.2458702176809311, 0.31476184725761414, 0.08014782518148422, -0.3720700442790985, 0.07490844279527664, 0.1526021808385849, -0.6964738368988037, -0.3958904445171356, 0.2245400846004486, 0.03604075685143471, 0.1382887065410614, 0.1757422238588333, -0.46633243560791016, -0.1097915843129158, -0.13043496012687683, 0.20032048225402832, 0.48504766821861267, 0.5723230242729187, 0.15693455934524536, 0.06111719086766243, 0.5659474730491638, -0.006002406589686871, 0.20675669610500336, -0.3170383870601654, -0.0629415437579155, 0.1846003234386444, -0.3324004113674164, -0.06472606956958771, 0.48875007033348083, -6.092693328857422, 0.22920534014701843, -0.23824572563171387, -0.22026288509368896, -0.20484864711761475, -0.5436765551567078, -0.4136310815811157, -0.5790757536888123, 0.0688653215765953, -0.4160555303096771, -0.10541250556707382, 0.25106340646743774, -0.30699822306632996, -0.6826447248458862, 0.24975362420082092, 0.4182946979999542]</t>
+          <t>['high', 'high', 'low', 'medium', 'high', 'high']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[-0.5, -1.0, -0.5, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 3, 5, 4]</t>
+          <t>[40.0, 25.0, 50.0, 35.0, 35.0, 25.0]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'woman', 'man', 'woman', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[40.0, 25.0, 50.0, 35.0, 35.0, 25.0]</t>
+          <t>[1, 3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>['woman', 'woman', 'man', 'woman', 'woman', 'man']</t>
+          <t>[4, 5, 2, 5, 5, 4]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1, 1]</t>
+          <t>[5, 5, 3, 4, 4, 1]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 5, 5, 4]</t>
+          <t>[2, 5, 5, 5, 4, 5]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 4, 4, 1]</t>
+          <t>[1, 4, 3, 3, 1, 1]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[2, 5, 5, 5, 4, 5]</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>[1, 4, 3, 3, 1, 1]</t>
-        </is>
+          <t>[2, 3, 2, 3, 3, 1]</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[2, 3, 2, 3, 3, 1]</t>
+          <t>[5, 5, 2, 4, 4, 1]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 4, 4, 1]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
           <t>[0.16666667 0.16666667 0.         0.33333333 0.33333333]</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="S2" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -639,85 +627,78 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 5, 5, 2]</t>
+          <t>['NONE', 'immigrant, black,', '{}', '{}', 'bisexual', 'Veteran']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['NONE', 'immigrant, black,', '{}', '{}', 'bisexual', 'Veteran']</t>
+          <t>['far right', 'center', 'right', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[-0.23865552246570587, -0.010829821228981018, -0.3427557945251465, -0.016615455970168114, -0.21117283403873444, -0.4411826729774475, 0.4364631772041321, 0.7059902548789978, 0.23145662248134613, -0.152572363615036, -0.0015582522610202432, 0.12018317729234695, -0.08009852468967438, -0.2299690842628479, 0.4595593214035034, 0.46991848945617676, -0.22018025815486908, 0.35510697960853577, 0.3792630136013031, -0.21821320056915283, -0.33821743726730347, -0.2911166250705719, -0.04951826110482216, 0.08821132779121399, 0.10528499633073807, -0.24462629854679108, 0.1990652233362198, 0.08689547330141068, -0.11323270946741104, 0.24842196702957153, 0.11876145750284195, 0.4015060067176819, -0.3807241916656494, -0.5671370625495911, 0.5229836702346802, 0.04128618165850639, 0.3214308023452759, 0.10044792294502258, 0.49524039030075073, 0.011662776581943035, -0.4225563108921051, 0.15392033755779266, 0.13511088490486145, -0.1773427575826645, -0.016081521287560463, -0.6306270360946655, -2.972683906555176, -0.3842184245586395, 0.1775875687599182, -0.21688733994960785, 0.15993928909301758, 0.03363976255059242, -0.2719670534133911, 0.6099779605865479, 0.2668575942516327, -0.0016366979107260704, -0.7907623648643494, 0.3184547424316406, -0.0639013722538948, 0.1988631784915924, 0.1053488627076149, 0.08853162825107574, -0.09021614491939545, 0.05582569167017937, -0.1946340799331665, 0.349865198135376, 0.16618143022060394, 0.5217905640602112, -0.36878833174705505, 0.227683886885643, -0.8292006254196167, -0.30544593930244446, 0.415203720331192, -0.010700770653784275, 0.21682526171207428, -0.17636677622795105, -0.2816270887851715, 0.028139207512140274, -0.6641745567321777, 0.31440481543540955, 0.06385240703821182, 0.7592821717262268, -0.05014726519584656, -0.1270875781774521, 0.39260923862457275, 0.22981059551239014, -0.35371676087379456, -0.28340116143226624, 0.39684081077575684, 0.3068872392177582, -0.1639920324087143, 0.38112154603004456, 0.06568021327257156, 0.1923033893108368, 0.3618241250514984, 0.08511237800121307, 0.24492482841014862, -0.17580752074718475, 0.17305880784988403, 0.01426341850310564, -0.04038490727543831, -0.10322783887386322, -0.11527496576309204, -0.9892500042915344, 0.28952154517173767, 0.00789755117148161, -0.43279215693473816, -0.2125583440065384, 0.07706334441900253, -2.496359348297119, 0.36507341265678406, 0.40326789021492004, -0.11522410809993744, -0.07563931494951248, -0.07256369292736053, 0.591461181640625, 0.03341455012559891, -0.1225760355591774, 0.006797255016863346, 0.0978107899427414, -0.2432432919740677, 0.09191351383924484, -0.08786915242671967, -0.06396781653165817, -0.20351983606815338, -0.10848840326070786, 0.5870670080184937, 0.45276597142219543, 0.2161240577697754, 0.3123376965522766, 0.12066792696714401, 0.4261498749256134, 0.19562262296676636, -0.05591970309615135, -0.554650068283081, 0.4468939006328583, 0.4231131672859192, -0.2699168622493744, -0.36990201473236084, -0.3699575662612915, -0.49460533261299133, -0.7164525389671326, -2.3975608348846436, -0.22807423770427704, 0.7470007538795471, -0.005009414162486792, 0.8555521965026855, 0.14756594598293304, 0.10145561397075653, 0.5104460716247559, 0.18296070396900177, 0.3892830014228821, -0.3402976095676422, 0.07263892143964767, -0.2553551197052002, -0.5929832458496094, -0.09679276496171951, -0.022268980741500854, 0.26252326369285583, 0.4354752004146576, 0.45863962173461914, -0.4082118272781372, -0.22149480879306793, -0.20565609633922577, -0.02924984134733677, 0.3894319534301758, 0.1466740220785141, -0.0038278368301689625, -0.009690064936876297, -0.062392719089984894, 0.403400719165802, 0.08447334170341492, 0.41085872054100037, 0.07932120561599731, 0.32824447751045227, 0.28390517830848694, 0.08555379509925842, 0.4699075520038605, 0.3617648780345917, -0.33709052205085754, -0.3911312520503998, 0.7034289836883545, 0.18208298087120056, -0.3776429295539856, 0.32076478004455566, -0.1705021858215332, 0.3529176115989685, -0.17890290915966034, -0.43368762731552124, 0.20630693435668945, -0.14212289452552795, -0.3697109520435333, 0.3781496584415436, -0.02129518613219261, 0.1758241057395935, -0.03839853033423424, 0.2460901439189911, -0.4159998893737793, -0.13742198050022125, 0.4034433662891388, -0.0017206866759806871, 0.11836100369691849, -0.5319730043411255, -0.015644878149032593, -0.5830387473106384, 4.137516975402832, 0.3094938099384308, -0.3139713406562805, 0.232430100440979, 0.36891594529151917, -0.2321023792028427, 0.07430648058652878, -0.2793389856815338, -0.544319748878479, -0.1739927977323532, 0.31145578622817993, 0.2798785865306854, 0.20749807357788086, -0.2877606451511383, -0.6706778407096863, 0.2355126589536667, 0.053825635462999344, -0.3573841452598572, 0.18246982991695404, -0.2178962230682373, -0.04896717146039009, -0.5780768990516663, 0.508907675743103, 0.022129174321889877, -1.8640756607055664, -0.06006486713886261, -0.01940249465405941, -0.011426487937569618, 0.5976097583770752, -0.5503900647163391, 0.2736121714115143, -0.346232533454895, -0.14997626841068268, 0.13917821645736694, 0.05462288111448288, -0.08313457667827606, 0.2388381063938141, -0.13125520944595337, 0.4062872529029846, -0.5602743625640869, 0.148036926984787, 0.18006591498851776, -0.08564089238643646, 0.22210876643657684, 0.24711555242538452, 0.09679917991161346, 0.04330739751458168, 0.19956792891025543, -0.4352458417415619, 0.2821621894836426, 0.14485354721546173, -0.27072006464004517, 0.6974020004272461, -0.7102755904197693, -0.509850800037384, -0.1297227293252945, 0.10520698875188828, 0.13038146495819092, 0.05966318026185036, -0.5847799181938171, -0.012815878726541996, 0.0559811033308506, -0.2072010636329651, -0.3958917558193207, -0.07301603257656097, -0.1706426590681076, -0.4112142026424408, -0.6554821729660034, -3.4606082439422607, -0.4505578577518463, 0.3535152077674866, 0.21795830130577087, 0.5503778457641602, -0.45571333169937134, 0.244756281375885, 0.1786385029554367, 0.40831294655799866, -0.6174828410148621, 0.4295748472213745, 0.22039826214313507, -0.46700456738471985, 0.5301120281219482, -0.4021293520927429, 0.09744937717914581, 0.19663108885288239, -0.4585394561290741, -0.053665321320295334, -0.10171603411436081, -0.12132791429758072, 0.02575189806520939, 0.04839586839079857, 0.19481614232063293, 0.33983534574508667, 0.37205958366394043, -0.5461099147796631, -0.2745339572429657, -0.3404504954814911, -0.07694127410650253, 0.2172052264213562, -0.0693039521574974, 0.29665112495422363, -0.3321717381477356, -0.7745269536972046, -2.752885341644287, 0.02833152562379837, -0.9154942631721497, -0.14558035135269165, 0.050516001880168915, 0.26887980103492737, 0.8360748887062073, -0.2613942623138428, -0.8387166857719421, 0.4099607765674591, -0.15988202393054962, -0.33650630712509155, 0.23068365454673767, -0.05209086090326309, 0.6136752367019653, 0.12287218123674393, 0.6050608158111572, -0.33729591965675354, -0.08382662385702133, 0.3695060908794403, -0.1987949013710022, -0.25091299414634705, 0.014704350382089615, -0.27482444047927856, 0.4452791213989258, 0.8169498443603516, -0.6129271984100342, 0.043203532695770264, -0.2950538098812103, 0.26581570506095886, 0.21373912692070007, 0.08333097398281097, 0.17221516370773315, -0.31006956100463867, -0.38423827290534973, -0.49855658411979675, -0.02877519652247429, 0.440147340297699, 0.4738476276397705, 0.039556533098220825, 0.00020651447994168848, 0.8802301287651062, -0.5031458139419556, 0.4800051152706146, 0.6561199426651001, 0.2986615002155304, 0.009449180215597153, -0.056832436472177505, 0.5859430432319641, 0.038081977516412735, -0.3267090618610382, 0.2430018037557602, 1.021105170249939, 0.5328104496002197, -0.2790583074092865, 0.12116297334432602, 0.44303908944129944, 0.055156413465738297, 0.20158997178077698, 0.1632850021123886, 0.5787469148635864, -1.1302412748336792, 0.011463701725006104, -0.028572486713528633, -0.03314662352204323, -0.3334595263004303, 0.3550131320953369, -0.6998093128204346, 0.041159071028232574, 0.5284305214881897, -0.030011139810085297, 0.015118160285055637, -0.058122023940086365, -1.1077970266342163, 0.29243308305740356, -0.009597123600542545, -0.5981431603431702, 0.15506263077259064, 0.09719842672348022, 0.16029834747314453, -0.2055785208940506, 0.005310871172696352, -0.5125579833984375, 0.5828375220298767, -0.042568389326334, 0.036283399909734726, 0.2057057023048401, 0.14965775609016418, -0.5626634359359741, -0.26758766174316406, -0.09555655717849731, 0.374002605676651, 0.08565455675125122, 0.22252799570560455, -0.6103253960609436, 0.060164619237184525, 0.31034448742866516, -0.7343676090240479, 0.5406062602996826, -0.17215603590011597, -0.18484088778495789, -0.5120919942855835, -0.21251754462718964, 0.40042543411254883, -0.18970246613025665, 0.09348214417695999, -0.2245819866657257, 0.08866406977176666, 0.046630050987005234, 0.2158535271883011, -0.10721246898174286, -0.13341288268566132, 0.14587734639644623, 0.08249414712190628, 0.5649272799491882, -0.14420677721500397, -0.33264443278312683, 0.8283772468566895, 0.04065318778157234, 0.2628827691078186, 0.3802907168865204, -0.1362864226102829, -0.03234979510307312, 0.1291118860244751, -0.538250744342804, -0.10033473372459412, 0.3464161157608032, -0.09426198154687881, -0.10375037789344788, -0.17787356674671173, 0.19622911512851715, -0.011028098873794079, -0.36287957429885864, -0.0919802114367485, 0.3235538601875305, -0.4050186574459076, -0.29519060254096985, -0.04011686146259308, 0.02288012020289898, -0.17816020548343658, 0.19127880036830902, 0.12230944633483887, -0.44966810941696167, 0.12281984835863113, -0.25646182894706726, 0.5020130276679993, 0.1353110820055008, 0.18326540291309357, -0.13722358644008636, 0.4929110109806061, 0.09941966086626053, -0.04519486054778099, 0.07773467153310776, -0.6330893039703369, 0.20935624837875366, 0.06194647029042244, -0.28404223918914795, -0.15165627002716064, 0.08671662211418152, 0.04524672031402588, 0.07162400335073471, 0.08604179322719574, -1.8901396989822388, -0.055038295686244965, 0.9291348457336426, 0.24967291951179504, 0.17066332697868347, -0.3645111322402954, -0.9612534642219543, 0.7932508587837219, 0.06981480121612549, -0.11460059136152267, -0.2500811219215393, -0.017728297039866447, 0.3261817395687103, -0.20288707315921783, 0.15538430213928223, -0.056533556431531906, 0.12313617020845413, -0.5721607208251953, -0.2647010385990143, -0.5064495205879211, -0.11994465440511703, 0.4465426206588745, -0.024878621101379395, -0.07068212330341339, -0.17200791835784912, -0.2310395985841751, -0.13409434258937836, 0.4377462565898895, -0.42826902866363525, 0.16460464894771576, -0.029133014380931854, -0.4937192499637604, -0.6092245578765869, 0.06684909760951996, -0.17055976390838623, -0.10296643525362015, 0.0433012992143631, 0.1807985156774521, 0.7243674993515015, 0.4382544159889221, -0.17546167969703674, 0.5434497594833374, 0.26702189445495605, 0.5115852355957031, 0.38919371366500854, 0.3789190649986267, -0.20121121406555176, 0.5454758405685425, -0.23940253257751465, -0.5761730074882507, -0.06595935672521591, -0.10482455790042877, -0.24011780321598053, -0.17918451130390167, -0.0069169653579592705, -0.4105442464351654, 0.2089005559682846, 0.09614789485931396, -0.1215943843126297, -0.15066249668598175, 0.25564736127853394, -0.04626299440860748, -0.12636393308639526, -0.10381495952606201, -0.1616847962141037, -0.7406570315361023, -0.19040921330451965, -0.3880390524864197, -0.6128414273262024, 0.16388781368732452, 0.8180056214332581, 0.03560421243309975, -0.7711693644523621, 0.23688499629497528, -0.20526058971881866, 0.19891177117824554, -0.10074252635240555, -0.15611475706100464, 0.4232900142669678, -0.009151346981525421, 0.03455838933587074, -0.558983325958252, -0.16145701706409454, 0.4519580006599426, 0.17266222834587097, 0.15930144488811493, -0.3518371284008026, -0.09538035094738007, 0.1537223756313324, -0.5754009485244751, -0.5197770595550537, -0.8986712098121643, 0.0821528360247612, 0.3768252432346344, 0.04547995701432228, 0.013962533324956894, 0.5739200711250305, 0.20645353198051453, 0.28789788484573364, 0.21558751165866852, -0.08442416042089462, 0.40757209062576294, 0.25746214389801025, 0.09231823682785034, -0.02093975991010666, 0.49352386593818665, 0.3884502053260803, -0.17220202088356018, -0.5460310578346252, 0.04865601658821106, 0.012823290191590786, -0.191717267036438, -0.14678330719470978, -0.24975553154945374, 0.4332559108734131, -0.29453638195991516, 0.27394863963127136, -0.39592602849006653, 1.8473483324050903, 0.5689423680305481, 0.565788984298706, -0.48159825801849365, 0.2617851197719574, -0.0078467708081007, -0.21112288534641266, 0.43531039357185364, -0.5337661504745483, 0.47446444630622864, -0.5235084295272827, 0.29927942156791687, -0.17160530388355255, 0.13955725729465485, 0.850579023361206, 0.5463907718658447, 0.17727303504943848, -0.4149850606918335, -0.47021734714508057, 0.2658638060092926, -0.18041817843914032, 0.7585462331771851, 0.5027549266815186, -0.1750512421131134, 0.24066510796546936, 0.5917224884033203, 0.08643712103366852, -0.1772301346063614, 0.5960316061973572, 0.6311112642288208, -0.25464028120040894, 0.3064397871494293, -0.0642613023519516, 0.36249151825904846, -0.18373256921768188, -0.04113156720995903, -0.03880010172724724, -0.28575393557548523, -0.2728617489337921, -0.08457447588443756, 0.40312957763671875, -0.6190091371536255, 0.6101505160331726, 0.0628669336438179, -0.2658300995826721, 0.404998779296875, -0.4632895290851593, -0.4754200279712677, 0.540643572807312, 0.49972906708717346, 0.3251960277557373, 0.30748674273490906, -0.18879392743110657, 0.018352126702666283, -0.20871934294700623, 0.08761157840490341, 0.09749988466501236, -0.3829419016838074, -0.770639181137085, 0.5441298484802246, -0.7234109044075012, 0.43869465589523315, 0.18309953808784485, 0.0342855341732502, 0.04812959209084511, -0.16041934490203857, -0.2549888491630554, 0.38040852546691895, 0.039829403162002563, -0.39366477727890015, -0.08025473356246948, 0.134464830160141, 0.3558257520198822, 0.08952924609184265, 0.4428568482398987, 0.23610182106494904, 0.05751044675707817, 0.27161914110183716, -0.6313323378562927, -2.681205987930298, 0.25960323214530945, 0.21764765679836273, 0.6248948574066162, -0.11001681536436081, 0.868199348449707, 0.15613244473934174, -0.12119876593351364, 0.23844681680202484, 0.016205504536628723, 0.22127553820610046, 0.22179032862186432, 0.4947252571582794, -0.3860308825969696, -0.10042936354875565, 0.3678501844406128, 0.21135713160037994, -0.07920871675014496, 0.1051606610417366, 0.20387470722198486, -0.011186116375029087, -0.0008449157467111945, -0.6307321190834045, -0.5731149315834045, -0.536720335483551, 0.2907578647136688, 0.4484100341796875, 0.02729133702814579, 0.2671217620372772, 0.9428532719612122, -0.5737543106079102, 0.37146109342575073, 0.2229190319776535, 0.015168875455856323, -0.15955471992492676, -0.062036603689193726, 0.050234172493219376, 0.48300111293792725, 0.471371591091156, 0.32268431782722473, -0.597777247428894, 0.3932960331439972, -0.3903253376483917, 0.024402309209108353, -0.12761127948760986, 0.08255546540021896, 0.579547107219696, -0.29206106066703796, 0.3929332494735718, -0.48855626583099365, -0.2439076155424118, -0.29981058835983276, 0.3942961096763611, 0.0892716571688652, 0.37502196431159973, 0.31374695897102356, 0.6493255496025085, -0.41805875301361084, -0.326729416847229, -0.24914808571338654, -0.02936602383852005, 0.3250085711479187, 0.1081453189253807, 0.19832690060138702, 0.5818192362785339, -0.4731423556804657, -0.1505928933620453, -0.009927934966981411, -0.041961491107940674, -0.3568946421146393, -0.1771855652332306, 0.16731122136116028, 0.35572680830955505, 0.361714243888855, 0.15078915655612946, 0.33942410349845886, -0.05368345230817795, 0.3580072224140167, 0.5340952277183533, -0.18618276715278625, -0.4159964323043823, -0.16020172834396362, -0.10794807970523834, 0.33182626962661743, 0.05558139830827713, -7.19006872177124, -0.2463415116071701, -0.6540901064872742, -0.41857531666755676, 0.017313294112682343, -0.3265291750431061, 0.1698891818523407, -0.1522865891456604, 0.2211635410785675, -0.3050689697265625, -0.10560674220323563, 0.3039934039115906, -0.04149143770337105, -0.1919836550951004, 0.3351425230503082, 0.49573075771331787]</t>
+          <t>['medium', 'medium', 'high', 'medium', 'medium', 'high']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[1.0, 0.0, 0.5, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 3, 3, 5]</t>
+          <t>[45.0, 35.0, 35.0, 45.0, 40.0, 35.0]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'woman', 'man', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[45.0, 35.0, 35.0, 45.0, 40.0, 35.0]</t>
+          <t>[5, 1, 1, 4, 1, 1]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'woman', 'man', 'woman', 'man']</t>
+          <t>[4, 4, 4, 3, 5, 5]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[5, 1, 1, 4, 1, 1]</t>
+          <t>[3, 5, 5, 3, 5, 1]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 3, 5, 5]</t>
+          <t>[3, 4, 5, 4, 5, 5]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 3, 5, 1]</t>
+          <t>[5, 1, 2, 3, 1, 5]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 4, 5, 5]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>[5, 1, 2, 3, 1, 5]</t>
-        </is>
+          <t>[4, 1, 3, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[4, 1, 3, 1, 1, 1]</t>
+          <t>[2, 5, 5, 3, 5, 1]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[2, 5, 5, 3, 5, 1]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
           <t>[0.16666667 0.16666667 0.16666667 0.         0.5       ]</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="S3" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -737,85 +718,78 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[4, 4, 2, 3, 2, 3]</t>
+          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'right', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[-0.21125884354114532, 0.3873864412307739, -0.10591500997543335, -0.49510112404823303, -0.39583492279052734, -0.17614871263504028, 1.1094934940338135, 0.352042019367218, -0.2196292132139206, 0.07923385500907898, 0.13090214133262634, -0.004023713991045952, -0.5086208581924438, 0.3759450614452362, 0.683006227016449, 0.24985504150390625, -0.26498860120773315, 0.6137298345565796, -0.054206397384405136, 0.14870090782642365, -0.24567461013793945, -0.26228171586990356, 5.483338100020774e-05, -0.3055267035961151, -0.13675040006637573, 0.28118401765823364, 0.11821666359901428, 0.1384943723678589, -0.09906788915395737, 0.22440341114997864, -0.3228144943714142, 0.22735223174095154, -0.6155533194541931, -0.44256946444511414, 0.37209364771842957, 0.2221219837665558, -0.13368570804595947, 0.38885781168937683, 0.41832396388053894, -0.09401026368141174, -0.323332279920578, 0.04094374552369118, -0.36946338415145874, -0.35311615467071533, -0.16341473162174225, -0.5024817585945129, -3.940455436706543, 0.1649554967880249, -0.36220115423202515, -0.9215824604034424, 0.3655078709125519, -0.5515931248664856, -0.42573416233062744, 0.35368484258651733, -0.5535209774971008, 0.5693815350532532, 0.06854499876499176, -0.12710653245449066, 0.057181451469659805, 0.25359535217285156, 0.17235781252384186, 0.104339599609375, 0.1017574667930603, 0.5013389587402344, -0.0291672945022583, -0.07536215335130692, -0.4778221845626831, 1.0079009532928467, -0.9146602749824524, 0.34735703468322754, -0.7450888752937317, -0.5155202746391296, 0.5811936259269714, -0.05183873325586319, 0.20004476606845856, -0.3078252077102661, -0.07813705503940582, 0.5415634512901306, -0.3451133072376251, 0.5252678394317627, -0.09472861140966415, 0.15391650795936584, -0.22079893946647644, 0.12320276349782944, -0.19480369985103607, 0.6295668482780457, 0.09545701742172241, -0.12174694985151291, 0.18397636711597443, 0.2864932715892792, 0.030456747859716415, -0.4278896152973175, -0.01406465657055378, -0.06906966865062714, 0.3352798521518707, 0.4101865589618683, 0.4041191339492798, 0.24744866788387299, 0.23528586328029633, 0.21968628466129303, 0.4273114800453186, -0.18263240158557892, 0.18868714570999146, -0.5704470276832581, -0.42860525846481323, -0.11795332282781601, -0.10927407443523407, -0.3859090209007263, -0.01572844758629799, -1.7099943161010742, 0.5633503794670105, -0.30344584584236145, -0.1941594034433365, -0.46335673332214355, -0.2012849897146225, 0.5534756183624268, 0.8341748118400574, -0.739448070526123, 0.3143814504146576, 0.45155104994773865, -0.4510174095630646, 0.10017119348049164, 0.4217289686203003, -0.45460423827171326, 0.0562923364341259, 0.24584411084651947, 0.5908433198928833, 0.1610453724861145, 0.7346426248550415, 0.2892630994319916, 0.28166162967681885, 0.586796760559082, 0.03187180683016777, -0.5220937132835388, -0.32132285833358765, 0.0009224824607372284, 0.06757019460201263, -0.08650773018598557, -0.21771936118602753, -0.5156198740005493, -0.49582356214523315, -0.3456652760505676, -2.4797251224517822, 0.30015265941619873, 0.5858224034309387, 0.30679240822792053, -0.5438787341117859, -0.687059760093689, 0.07732435315847397, 0.43892574310302734, 0.10388677567243576, -0.087368905544281, 0.4251614809036255, 0.15153074264526367, -0.5498623251914978, 0.15741735696792603, -0.5309491753578186, -0.4363288879394531, 0.10766762495040894, 0.5097228288650513, -0.001523936982266605, -0.04070230945944786, 0.1476570963859558, 0.3964769244194031, -0.17863984405994415, 0.04273699223995209, 0.09199336916208267, 0.31579795479774475, -0.2195052057504654, -0.44725731015205383, 0.013371480628848076, -0.18418753147125244, 1.2113890647888184, 0.2704527974128723, 0.2911255657672882, -0.5857318639755249, 1.0597840547561646, 0.09735114872455597, -0.0840483233332634, 0.06055837497115135, -0.5722338557243347, 0.09601481258869171, 0.3374719023704529, 0.04082934558391571, 0.5350168943405151, -0.039963118731975555, 1.0022172927856445, 0.06406227499246597, -0.09347838908433914, 0.6315798163414001, -0.7732617259025574, 0.08751064538955688, 0.5550258755683899, 0.5033051371574402, 0.7627608776092529, -0.33633825182914734, 0.5130428671836853, -0.550222635269165, 0.24054624140262604, 0.030077701434493065, -0.1331295520067215, -0.8243975639343262, 0.2967318892478943, -0.08136992901563644, -0.35096579790115356, 4.014882564544678, -0.13617923855781555, -0.025125036016106606, 0.09674732387065887, 0.6193134784698486, -0.4663970470428467, -0.3231520354747772, -0.14402812719345093, -0.4975079596042633, -0.3424013555049896, 0.3042040169239044, 0.9067620038986206, -0.24200096726417542, -0.2547069489955902, 0.3333301544189453, 0.43684715032577515, -0.010374858044087887, -0.3660311698913574, 0.13030846416950226, -0.07627756148576736, -0.0743500217795372, -0.08100827783346176, -0.3187101185321808, -0.11033247411251068, -2.171970844268799, 0.18268081545829773, -0.2554493546485901, 0.1724359393119812, 0.5655346512794495, -0.19738343358039856, 0.5166770219802856, -0.3036684989929199, -0.22453203797340393, -0.09427780658006668, -0.25193873047828674, -0.4642512798309326, 0.6536238193511963, 0.002125623868778348, 0.010744662024080753, -0.1050962507724762, 0.5935257077217102, 0.8993897438049316, -0.7975585460662842, 0.5254186391830444, 0.29340821504592896, 0.1928490549325943, 0.2271631807088852, -0.03857133910059929, -0.38614383339881897, 0.5382639765739441, 0.22852137684822083, 0.1396145075559616, 0.02098257467150688, -0.4968305230140686, -0.34660768508911133, -0.34295719861984253, 0.2835308909416199, 0.14950814843177795, 0.07796168327331543, -0.8536006212234497, 0.28681766986846924, 0.31501495838165283, -0.14494889974594116, -0.6175721883773804, -0.07561266422271729, 0.4523596167564392, 0.022684501484036446, -0.0014741673367097974, -2.288633346557617, 0.08967548608779907, 0.5071180462837219, 0.1317947953939438, 0.3785456717014313, -0.24094414710998535, -0.15232183039188385, -0.02714705467224121, 0.6904794573783875, -1.1198973655700684, 0.2861855924129486, 0.09748189151287079, 0.22777271270751953, 0.07579760253429413, -0.43137723207473755, 0.26280367374420166, -0.3249860405921936, -0.07621291279792786, -0.18028174340724945, -0.15446452796459198, 0.6451237797737122, -0.013823162764310837, -0.1275031566619873, 0.25084182620048523, -0.06465322524309158, -0.10635578632354736, 0.22302885353565216, -0.22209544479846954, -0.20886088907718658, -0.15777543187141418, 0.5049566030502319, -0.2442575842142105, 0.3398545980453491, 0.29132476449012756, -0.6910931468009949, -2.908487558364868, 0.1513819843530655, -0.009152138605713844, -0.6260948777198792, 0.44516927003860474, -0.228395476937294, 0.5125240087509155, -0.08624736964702606, -0.42801633477211, 0.2045246958732605, 0.016181951388716698, -0.5176344513893127, 0.33871155977249146, -0.09752962738275528, 0.3702034652233124, 0.23775072395801544, 0.5394293665885925, -0.24766969680786133, 0.16114801168441772, -0.22535407543182373, 0.13708986341953278, 0.5537582635879517, 0.46552103757858276, -0.2660842835903168, 0.6365756988525391, 0.5650895237922668, -0.5422074794769287, -0.2253655046224594, 0.06756661832332611, 0.29181239008903503, -0.005095140542834997, 0.15714477002620697, 0.2778523564338684, -0.22586199641227722, -0.43058550357818604, -0.22791989147663116, 0.7109541296958923, 0.07912714779376984, 0.5594931840896606, -0.052689943462610245, 0.23127011954784393, 0.38584545254707336, -0.35616764426231384, -0.2224421203136444, 0.5482478737831116, -0.0362299419939518, -0.11198200285434723, -0.36789971590042114, 0.02581310272216797, 0.006033970508724451, -0.40396013855934143, -0.16319862008094788, 0.8699795007705688, 0.39148324728012085, 0.06912574917078018, -0.686301052570343, -0.1639796644449234, 0.38493403792381287, -0.12191465497016907, -0.13438697159290314, 1.072497844696045, -0.1251239776611328, 0.26308366656303406, -0.061306361109018326, 0.18988682329654694, -0.1727786809206009, 0.2469319999217987, -0.8513615727424622, 0.41082698106765747, 0.651781439781189, -0.18743787705898285, 0.3060099184513092, -0.32871007919311523, -1.754679799079895, -0.08500178903341293, 0.1268479973077774, -0.029168011620640755, 0.4008169174194336, -0.19337719678878784, 0.46721169352531433, -0.4410792291164398, -0.079254150390625, -0.6149993538856506, 0.40751343965530396, -0.6288583278656006, -0.2602507770061493, 0.2614765465259552, 0.10643851011991501, -0.6363580822944641, -0.09428302198648453, 0.15125635266304016, 0.4375327527523041, 0.28947874903678894, 0.6679375171661377, -0.5787221193313599, 0.3579327166080475, 0.4743964672088623, -1.09674870967865, 0.3350537419319153, -0.04782792925834656, 0.5762452483177185, -0.31830620765686035, 0.0721026286482811, -0.01903846114873886, -0.09698936343193054, -0.06166106462478638, -0.4213651716709137, 1.1533199548721313, 0.35860782861709595, 0.4018175005912781, -0.6533368825912476, 0.038807693868875504, -0.5266872644424438, 0.3842666447162628, 0.5895688533782959, -0.3318737745285034, -0.18987606465816498, 0.6357356905937195, 0.15082040429115295, 0.34976473450660706, 0.522263765335083, 0.23429609835147858, -0.3230588734149933, -0.495937705039978, -0.7117923498153687, -0.09437722712755203, -0.4241066873073578, -0.35881152749061584, -0.14162705838680267, -0.3558501899242401, 0.4965023398399353, -0.17212344706058502, -0.42067185044288635, -0.2799794673919678, 0.35409173369407654, -0.3456316292285919, -0.03180784359574318, -0.22006234526634216, 0.5266314148902893, 0.07705876976251602, 0.3114147186279297, -0.04367508366703987, -0.09002382308244705, 0.059578679502010345, -0.6153950095176697, 0.750723123550415, -0.5204827189445496, -0.3457958698272705, 0.10262206196784973, 0.8542342782020569, -0.5469550490379333, -0.32544317841529846, -0.11548957228660583, -1.176137089729309, 0.14725945889949799, 0.08948493003845215, -0.404428631067276, -0.3665684461593628, -0.023328645154833794, 0.0075372448191046715, -0.11349441111087799, -0.0914735496044159, -2.1025731563568115, 0.7733333110809326, 0.5951759815216064, 0.12108513712882996, 0.6873926520347595, -0.23330338299274445, -0.5536894202232361, 0.27877169847488403, -0.17169888317584991, -0.20577198266983032, -0.5043649077415466, -0.2291487753391266, -0.1005282998085022, 0.5595203042030334, 0.2905910015106201, 0.03710019960999489, 0.04175100848078728, -0.3017989993095398, -0.2720787227153778, 0.008635221049189568, -0.171005517244339, 0.4035530090332031, 0.6994035243988037, -0.19116896390914917, 0.2189612090587616, -0.3433670997619629, -0.3398846387863159, 0.6621758937835693, -0.2278931438922882, 0.1103542149066925, 0.008073048666119576, -0.16314975917339325, -1.0587114095687866, -0.14943046867847443, 0.35096579790115356, 0.5269619226455688, 0.4278184175491333, 0.41523000597953796, 0.7492819428443909, 0.6990306973457336, -0.09943711757659912, 0.26791641116142273, 0.12570549547672272, 0.23976346850395203, 0.3982456624507904, 0.18916043639183044, -0.04959447309374809, 0.7512801289558411, 0.5683331489562988, -0.9997878670692444, -0.6567490100860596, -0.5473501086235046, 0.17262673377990723, -0.38682693243026733, -0.04478880763053894, -0.18564824759960175, 0.24973297119140625, -0.19886045157909393, -0.6020978689193726, 0.14705634117126465, -0.5718240141868591, 0.2344328761100769, -0.4482423961162567, 0.036808013916015625, -0.9291751980781555, -0.5348473191261292, -0.11970909684896469, -0.5524624586105347, 0.11737512797117233, 0.05391831323504448, 0.40552499890327454, 0.5191378593444824, -0.20448938012123108, 0.3378540277481079, -0.091473788022995, 0.6556528210639954, -0.2204299122095108, -0.050560809671878815, 0.13121475279331207, -0.4224301278591156, 0.3839162588119507, -0.8434243202209473, 0.052382051944732666, 0.6760375499725342, -0.2159755676984787, 0.33218103647232056, 0.03316415846347809, -0.3483675718307495, 0.4160291850566864, -0.4619103968143463, -0.8446126580238342, -0.36392664909362793, -0.09566138684749603, 0.14179684221744537, 0.11272168159484863, -0.3819887638092041, 0.06495022028684616, 0.3547664284706116, 0.16172368824481964, -0.20106655359268188, -0.2541577219963074, -0.009522918611764908, 0.2502920627593994, -0.09644719958305359, 0.6956743001937866, 0.06548827141523361, 0.08212684094905853, 0.05064765736460686, -0.5962313413619995, -0.25817060470581055, 0.3649195432662964, -0.07196459174156189, -0.731868326663971, -0.25882795453071594, 0.015398400835692883, -0.21035191416740417, -0.1890377551317215, -0.13875463604927063, 1.287889003753662, 0.6066777110099792, 0.025516780093312263, -0.4405191242694855, 0.5549365878105164, -0.04259040579199791, 0.052725013345479965, 0.14887304604053497, -0.49027255177497864, 0.6974376440048218, -0.33647093176841736, 0.33873450756073, -1.008508324623108, 0.18365974724292755, 0.8044003248214722, 0.15322305262088776, -0.18597063422203064, -0.2216981053352356, -0.6638882160186768, 0.38122957944869995, 0.08427085727453232, 0.4870474636554718, 0.7882228493690491, -0.3408587574958801, 0.3233746886253357, 0.4749529957771301, 0.022890238091349602, -0.6756587028503418, 0.19286063313484192, 0.7542376518249512, -0.9433748722076416, 0.09898178279399872, 0.3822205364704132, 0.2169404923915863, -0.7871291637420654, 0.3523874580860138, -0.07222610712051392, -0.04534586891531944, -0.332240492105484, 0.15530738234519958, 0.46414098143577576, -0.5281242728233337, 0.7346698641777039, -0.07436840981245041, -0.4534977078437805, 0.5219605565071106, -0.6175304651260376, -0.312715083360672, 0.8132122755050659, 0.45817187428474426, 0.27645668387413025, -0.293760746717453, -0.6709722280502319, -0.08897077292203903, 0.01787392422556877, -0.2942255437374115, -0.039463743567466736, -0.43543168902397156, -0.05921684205532074, -0.039429135620594025, -0.32228702306747437, 0.8163896203041077, -0.3681623637676239, -0.45387977361679077, -0.19792404770851135, 0.2435891479253769, -0.25389203429222107, -0.8631097078323364, 0.21728083491325378, -0.2285049706697464, 0.12304412573575974, 0.5920047760009766, -0.36907342076301575, 0.3016858398914337, 0.4227246046066284, 0.7804798483848572, -0.07372201234102249, -0.33181533217430115, -0.3210548758506775, -2.1725311279296875, 0.4734426438808441, 0.2596258819103241, 0.5121161341667175, 0.0304965041577816, 0.5313918590545654, 0.37933146953582764, 0.040394239127635956, 0.5401599407196045, -0.4481537342071533, 0.7286747694015503, 0.43629199266433716, 0.6158676743507385, -0.08364219218492508, 0.26254868507385254, 0.45344603061676025, 0.4821305274963379, -0.5515859127044678, -0.21682390570640564, -0.8227020502090454, 0.25266432762145996, 0.22155281901359558, -0.1558850109577179, -0.5794478058815002, -0.5557861924171448, 0.2619575560092926, -0.01064428873360157, -0.6010352373123169, 0.14252832531929016, 0.5075100064277649, -0.19666051864624023, 0.3609006404876709, 0.14405232667922974, -0.03945882245898247, 0.07971286028623581, -0.0041956366039812565, -0.48740777373313904, 0.30196911096572876, 0.24411974847316742, -0.22565700113773346, 0.2179737687110901, 0.6135339140892029, 0.17475059628486633, -0.09475145488977432, 0.06354569643735886, -0.3024600148200989, 0.6185099482536316, 0.38872411847114563, 0.7403309941291809, 0.1678246706724167, 0.16833695769309998, -0.2887340486049652, 0.08358090370893478, -0.295322984457016, 0.04323742911219597, 0.6302679777145386, 0.3277529776096344, -0.010371243581175804, -0.3188953995704651, -1.0381511449813843, 0.2349962443113327, 0.23358838260173798, -0.08766718208789825, -0.1317041963338852, 0.6782746315002441, -0.44771650433540344, 0.16268612444400787, 0.5309415459632874, -0.05261524021625519, -0.6085698008537292, -0.3469180464744568, 0.013448294252157211, 0.41638174653053284, 0.304054856300354, -0.39052996039390564, -0.2595655024051666, 0.4874671995639801, 0.11781700700521469, 0.31547439098358154, -0.018231341615319252, -0.2393025904893875, 0.4477918744087219, -0.14312033355236053, 0.2463812530040741, 0.5577985048294067, -5.922809600830078, 0.10762573778629303, -0.5943220257759094, -0.8716166615486145, -0.08273284882307053, -0.8498809933662415, 0.20703645050525665, -0.35524094104766846, 0.012291940860450268, -0.3562879264354706, 0.685897946357727, 0.5103698968887329, -0.27372920513153076, -0.6473087072372437, 0.7380377650260925, 0.36033278703689575]</t>
+          <t>['medium', 'high', 'low', 'high', 'high', 'medium']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[3, 5, 2, 4, 4, 3]</t>
+          <t>[30.0, 30.0, 40.0, 35.0, 35.0, 45.0]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'woman', 'woman', 'woman']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 40.0, 35.0, 35.0, 45.0]</t>
+          <t>[1, 1, 5, 1, 2, 1]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'woman', 'woman', 'woman']</t>
+          <t>[3, 3, 2, 3, 3, 4]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 1, 2, 1]</t>
+          <t>[5, 4, 3, 2, 3, 2]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[3, 3, 2, 3, 3, 4]</t>
+          <t>[5, 3, 5, 5, 4, 4]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[5, 4, 3, 2, 3, 2]</t>
+          <t>[1, 1, 4, 1, 2, 1]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 5, 4, 4]</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>[1, 1, 4, 1, 2, 1]</t>
-        </is>
+          <t>[1, 1, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[4, 4, 3, 2, 2, 2]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[4, 4, 3, 2, 2, 2]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
           <t>[0.         0.5        0.16666667 0.33333333 0.        ]</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="S4" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -835,85 +809,78 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[3, 1, 5, 4, 2, 3]</t>
+          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[nan, '{}', '{}', '{}', '{}', '{}']</t>
+          <t>['left', 'left', 'right', 'center', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[0.22918452322483063, 0.273483544588089, -0.15212084352970123, -0.19789855182170868, -0.3836861252784729, -0.1907900869846344, 0.3080484867095947, 0.5435482263565063, -0.13244785368442535, -0.15225762128829956, 0.20399169623851776, 0.002281149150803685, 0.038625843822956085, 0.1377333700656891, 0.21500368416309357, -0.04063894972205162, 0.08953451365232468, 0.2827061116695404, -0.03622343763709068, -0.1439571976661682, -0.041162047535181046, -0.07272978872060776, -0.08390731364488602, -0.14783616364002228, 0.16635267436504364, -0.07852919399738312, -0.03463895618915558, -0.01613367162644863, -0.035462673753499985, 0.17997418344020844, 0.20136046409606934, -0.022369876503944397, 0.03672736883163452, 0.01895913854241371, -0.027148578315973282, -0.020193753764033318, 0.04333626851439476, -0.19213025271892548, 0.08022329956293106, 0.011004526168107986, -0.0463508702814579, -0.18946737051010132, 0.1746690720319748, 0.1368151307106018, 0.08596109598875046, -0.2477170079946518, -2.344353199005127, -0.06259842216968536, -0.16055245697498322, -0.06736588478088379, 0.2566932141780853, 0.033677615225315094, 0.012257632799446583, 0.02994157187640667, 0.2811981439590454, 0.1607358604669571, 0.01158539392054081, 0.5264602303504944, 0.10596880316734314, 0.3000505864620209, 0.2912573218345642, 0.27176016569137573, -0.15183745324611664, 0.15231966972351074, -0.018591351807117462, 0.2618381381034851, -0.04030432924628258, 0.12455097585916519, -0.06265154480934143, 0.40873247385025024, -0.13892726600170135, -0.26372775435447693, 0.17076271772384644, -0.12192851305007935, 0.1802675426006317, -0.3422262668609619, -0.03891006112098694, 0.0773678794503212, 0.027236944064497948, 0.015203841030597687, 0.05304668843746185, 0.2772364318370819, 0.21259304881095886, 0.13158875703811646, -0.04682908207178116, 0.16325390338897705, -0.1838987022638321, -0.16516724228858948, 0.11791009455919266, 0.4334457814693451, -0.24176523089408875, 0.3269510269165039, -0.1681821048259735, 0.3647841215133667, 0.2227284461259842, -0.19531574845314026, -0.06897492706775665, 0.024348601698875427, 0.13459473848342896, 0.05194776505231857, -0.07228798419237137, -0.06569243967533112, -0.01966489665210247, -0.09857936948537827, 0.04761309176683426, -0.1191982626914978, -0.10137476027011871, -0.2631251811981201, 0.056515421718358994, -2.8213071823120117, 0.18451513350009918, 0.1292315125465393, -0.09210583567619324, -0.21568413078784943, 0.03427771106362343, 0.26240265369415283, 0.30602243542671204, 0.044912464916706085, 0.19220295548439026, -0.025520652532577515, -0.2107352763414383, 0.4772547483444214, 0.07953717559576035, -0.06826318800449371, 0.17207854986190796, -0.11770213395357132, 0.19349731504917145, -0.05963229760527611, 0.031138520687818527, -0.0037247631698846817, 0.03990636765956879, 0.37348461151123047, -0.006570666097104549, -0.09873857349157333, -0.2825653553009033, -0.06304862350225449, 0.19143719971179962, -0.17609669268131256, 0.05137830600142479, -0.18260490894317627, -0.1921263039112091, -0.18962140381336212, -3.4708690643310547, 0.06987500935792923, 0.23859180510044098, -0.01691829040646553, -0.11282467842102051, -0.02548673003911972, 0.18782734870910645, 0.0927526205778122, 0.0008378406055271626, 0.002498394111171365, -0.1604527235031128, 0.14425277709960938, -0.10017437487840652, -0.22044220566749573, -0.049417149275541306, -0.108359195291996, 0.15598800778388977, 0.16017277538776398, 0.22009997069835663, -0.4289569556713104, 0.03428249433636665, -0.402191698551178, -0.05830257013440132, -0.16821351647377014, 0.3670772910118103, 0.17218102514743805, 0.09978044778108597, 0.04358445107936859, 0.1778215616941452, 0.10161430388689041, 0.19568690657615662, 0.14574484527111053, -0.11957788467407227, -0.20310957729816437, 0.06141131743788719, 0.23603691160678864, -0.003091618185862899, 0.0652516707777977, -0.15790069103240967, 0.285179078578949, 0.2296474725008011, 0.1076817512512207, 0.2953503727912903, -0.016649702563881874, 0.22741861641407013, -0.09861968457698822, -0.33408111333847046, 0.3113890588283539, -0.14188911020755768, -0.17182976007461548, 0.24116083979606628, -0.03076828643679619, 0.2865302562713623, -0.23154929280281067, 0.06894894689321518, -0.44053176045417786, 0.03457041457295418, 0.34999966621398926, -0.14911805093288422, -0.023085802793502808, -0.21874603629112244, -0.18353058397769928, -0.0766199454665184, 4.066248893737793, 0.19750668108463287, 0.17614299058914185, 0.10394293814897537, 0.028302814811468124, 0.12285928428173065, -0.01378039363771677, -0.15871356427669525, -0.10168130695819855, -0.2648790776729584, -0.19020746648311615, -0.0007852162816561759, 0.15755227208137512, -0.15609382092952728, 0.105527363717556, 0.2511017620563507, 0.4217383563518524, -0.3047429621219635, 0.10417642444372177, 0.08063747733831406, -0.17724958062171936, -0.013159182853996754, 0.24630343914031982, 0.1700037568807602, -1.1569267511367798, 0.15632565319538116, -0.07690181583166122, -0.3469318449497223, 0.22587542235851288, -0.14218769967556, 0.15342682600021362, 0.06324835866689682, 0.0047822254709899426, 0.0027520046569406986, 0.0800105631351471, -0.23603570461273193, 0.11389423906803131, 0.11580293625593185, 0.07039409875869751, -0.15791526436805725, 0.4277607798576355, 0.013012128882110119, -0.08454809337854385, -0.07340878248214722, 0.3663457930088043, 0.1678367406129837, 0.055313028395175934, -0.06015994772315025, -0.08654280751943588, -0.02531999908387661, 0.08046542853116989, -0.05619712546467781, 0.07907784730195999, -0.3908730447292328, -0.2707376182079315, -0.19392657279968262, -0.1571253538131714, 0.011877807788550854, 0.13318566977977753, -0.1432165950536728, 0.03916694223880768, 0.08838175982236862, -0.04091454669833183, 0.18106509745121002, 0.07468094676733017, -0.026499072089791298, -0.08549512922763824, -0.2776702344417572, -4.735240936279297, -0.19308984279632568, -0.0026435377076268196, 0.16187725961208344, 0.337787926197052, -0.22542135417461395, 0.1462094932794571, 0.15218237042427063, 0.05843959376215935, -0.2673165500164032, 0.15891389548778534, 0.003184567904099822, -0.16662490367889404, 0.2892209589481354, -0.37593507766723633, 0.31314730644226074, 0.2952641546726227, -0.015340096317231655, -0.11382342129945755, -0.03737122565507889, 0.19266913831233978, 0.29595768451690674, -0.4233802855014801, 0.1089598536491394, -0.11833097040653229, -0.12594115734100342, -0.3478972613811493, -0.16216064989566803, 0.13224920630455017, -0.03504336625337601, 0.20905034244060516, -0.058991383761167526, -0.01716660149395466, -0.16253525018692017, -0.15692178905010223, -2.5067408084869385, 0.16859644651412964, -0.1830248087644577, -0.013990976847708225, 0.2571087181568146, -0.13848039507865906, 0.44406014680862427, -0.25076940655708313, -0.21220402419567108, 0.23830927908420563, 0.12714500725269318, 0.06008128449320793, 0.19003954529762268, -0.11128328740596771, 0.053869783878326416, 0.0717075988650322, -0.02621236816048622, -0.04124310985207558, 0.03796864673495293, 0.007401785347610712, 0.045934002846479416, 0.21757668256759644, -0.1385076493024826, 0.0985768586397171, 0.1401412934064865, 0.08529867231845856, -0.32563158869743347, 0.13817660510540009, 0.04625860974192619, -0.05869125947356224, 0.040399737656116486, -0.0021300402004271746, -0.03571871668100357, -0.037978921085596085, -0.05416740104556084, -0.22828805446624756, 0.011557421647012234, 0.23477868735790253, 0.2707619071006775, 0.10069304704666138, 0.06455064564943314, 0.2416071742773056, -0.24504147469997406, 0.2259558141231537, 0.19512903690338135, -0.04927444830536842, -0.16682979464530945, -0.3159969747066498, 0.15536952018737793, -0.12173391878604889, 0.29655206203460693, -0.07859780639410019, 0.991074800491333, 0.2581852674484253, 0.07498113811016083, -0.25931864976882935, 0.2357708066701889, 0.10472379624843597, -0.0808221772313118, 0.15401597321033478, 0.3226592540740967, -0.11763449758291245, 0.308453768491745, 0.12117408961057663, -0.058157116174697876, -0.2075534462928772, 0.09784714877605438, -0.4410179555416107, 0.10251123458147049, 0.006353528238832951, 0.08726365864276886, 0.16451334953308105, -0.19346554577350616, -0.6071445345878601, 0.13807207345962524, 0.18192008137702942, -0.28710493445396423, 0.28229668736457825, 0.006350586656481028, -0.008262930437922478, 0.08330028504133224, -0.0751255601644516, 0.03941776230931282, 0.15565188229084015, -0.13924852013587952, -0.08137383311986923, -0.008084855042397976, 0.23584312200546265, -0.11059167236089706, 0.14812728762626648, 0.04548393562436104, 0.2496754229068756, 0.13792337477207184, 0.0374084897339344, 0.1615171581506729, 0.241925448179245, 0.18973413109779358, -0.660447359085083, 0.022663556039333344, -0.06964053213596344, -0.14525718986988068, -0.3243461847305298, -0.13737273216247559, -0.05678886920213699, -0.09425409883260727, -0.08953500539064407, -0.09314372390508652, 0.4658240079879761, 0.02188664861023426, 0.11216916888952255, -0.06043481454253197, 0.2518777549266815, 0.14978691935539246, 0.047166600823402405, 0.4836185872554779, -0.19879604876041412, 0.00983451772481203, 0.25472670793533325, -0.016876833513379097, 0.07240386307239532, 0.18649829924106598, 0.06175834685564041, -0.15841032564640045, -0.06598778069019318, -0.021524900570511818, -0.061172422021627426, -0.15166616439819336, -0.16712039709091187, -0.10509836673736572, -0.16373270750045776, -0.09367343038320541, 0.06042187288403511, -0.17487797141075134, -0.3192612826824188, -0.19092023372650146, -0.29806432127952576, -0.3394107222557068, 0.08150870352983475, -0.16384100914001465, 0.16517503559589386, 0.06413284689188004, 0.02822532318532467, 0.031116114929318428, 0.0269265566021204, -0.052579037845134735, 0.4107775092124939, -0.11749983578920364, 0.008141882717609406, -0.019576864317059517, 0.44870758056640625, -0.001869186176918447, 0.08869930356740952, 0.1772569715976715, -0.35286617279052734, 0.02158971130847931, 0.39295560121536255, -0.1373969167470932, 0.126071035861969, 0.236458420753479, 0.45584461092948914, 0.08872019499540329, 0.05574769899249077, -1.2435872554779053, 0.15986399352550507, 0.20295989513397217, -0.0845378190279007, 0.083944171667099, -0.10458655655384064, -0.12030836194753647, 0.28513792157173157, 0.27472493052482605, 0.07713337242603302, -0.102178655564785, 0.053535640239715576, 0.08102519065141678, 0.09967910498380661, -0.0913471207022667, 0.04567474499344826, 0.5222405195236206, -0.10526308417320251, -0.09419088810682297, 0.02924215793609619, 0.38467445969581604, 0.0833292156457901, -0.16492880880832672, 0.03018476441502571, -0.052279599010944366, -0.09069083631038666, 0.04082100838422775, 0.3295574188232422, 0.1165064200758934, 0.1661399006843567, 0.03604914993047714, -0.3837491571903229, -0.4258173406124115, -0.05816371366381645, 0.058872953057289124, 0.05911361798644066, 0.2027420848608017, -0.04148967191576958, 0.400970995426178, 0.098755843937397, -0.3016614019870758, 0.3941855728626251, 0.32174399495124817, -0.05065835639834404, 0.12256903946399689, 0.1510491669178009, -0.13345471024513245, 0.19882772862911224, 0.18363557755947113, -0.3011561930179596, -0.12910470366477966, -0.08887439966201782, 0.040028177201747894, -0.21833853423595428, 0.1216159388422966, -0.2967831790447235, -0.04698147252202034, -0.12469076365232468, -0.0035825821105390787, 0.09378113597631454, 0.23953111469745636, 0.10761220008134842, -0.3760863244533539, 0.32013997435569763, -0.38431766629219055, -0.44468411803245544, 0.15349555015563965, -0.09897967427968979, -0.2636328339576721, 0.1597066968679428, 0.32082033157348633, 0.10537639260292053, -0.06518909335136414, -0.026979859918355942, -0.27850303053855896, 0.6038870811462402, -0.015231339260935783, 0.02629019506275654, 0.10647693276405334, -0.045474015176296234, 0.07692486047744751, -0.13121753931045532, -0.09933021664619446, -0.013704406097531319, -0.00840051844716072, 0.10461476445198059, 0.053878381848335266, -0.10940222442150116, -0.1322348266839981, -0.042749859392642975, -0.16597430408000946, -0.22987604141235352, 0.3477264642715454, 0.06776303797960281, -0.0718221589922905, -0.03050680086016655, 0.2217731475830078, -0.042090728878974915, -0.008569805882871151, 0.08686857670545578, -0.3390926420688629, 0.2427549511194229, 0.18032552301883698, 0.18720342218875885, -0.1170094758272171, 0.06249883025884628, 0.3327174186706543, 0.12434452772140503, -0.3982607126235962, -0.16565795242786407, 0.136601984500885, 0.1175423339009285, -0.23159727454185486, -0.06929469108581543, -0.09941068291664124, 0.15193277597427368, 0.6067447662353516, -0.21025551855564117, 2.5691003799438477, 0.09735524654388428, 0.04841286316514015, -0.16957557201385498, 0.33433055877685547, -0.009993803687393665, 0.05635907128453255, 0.008463334292173386, -0.28590768575668335, 0.1498531550168991, -0.15351498126983643, 0.22832201421260834, -0.18561652302742004, -0.07330531626939774, 0.20270700752735138, 0.038134634494781494, -0.10683707147836685, 0.09929152578115463, -0.4251340329647064, 0.05987965315580368, 0.015345602296292782, 0.10117854177951813, 0.04032253101468086, -0.41553419828414917, 0.13019104301929474, 0.12883643805980682, 0.04842640459537506, 0.1670030951499939, 0.11833424121141434, 0.041700005531311035, -0.013154657557606697, -0.1750863790512085, 0.09164533019065857, -0.11270712316036224, -0.11899132281541824, 0.16686439514160156, 0.10780595242977142, -0.02838055044412613, 0.09554137289524078, 0.05242367833852768, -0.14026758074760437, -0.28900906443595886, 0.3443026542663574, 0.08119072020053864, 0.11849469691514969, 0.1411663293838501, 0.10690546035766602, -0.1715940535068512, 0.27697885036468506, 0.2191087305545807, -0.08551342785358429, -0.05872929096221924, 0.16473639011383057, 0.05756821483373642, -0.04895227402448654, -0.13553348183631897, 0.2134152054786682, -0.33908817172050476, -0.21228879690170288, 0.2814304828643799, -0.16972611844539642, 0.011766787618398666, 0.3084530234336853, 0.24701665341854095, -0.039413318037986755, 0.1878434717655182, -0.10965820401906967, 0.08577235043048859, 0.14383913576602936, -0.04362509027123451, -0.1203022450208664, 0.09279090166091919, 0.19498924911022186, -0.03932106867432594, 0.12464964389801025, 0.038103096187114716, 0.34871381521224976, 0.003013468347489834, -0.15753310918807983, -3.6018760204315186, -0.1474754363298416, -0.19028142094612122, -0.0710202232003212, 0.09329880774021149, 0.16451436281204224, 0.26058074831962585, -0.020566949620842934, 0.056565798819065094, -0.02794678881764412, 0.09226146340370178, 0.19161827862262726, 0.2943497598171234, 0.23714002966880798, 0.18146705627441406, 0.17398184537887573, -0.10143087059259415, -0.24839641153812408, -0.05132479965686798, -0.1574881225824356, 0.07205453515052795, -0.025983238592743874, -0.12011702358722687, -0.13498617708683014, -0.06905066967010498, 0.10181138664484024, 0.010595100931823254, -0.01834605634212494, 0.049675460904836655, 0.13571138679981232, -0.07190175354480743, 0.11038622260093689, -0.027111658826470375, -0.0017911066533997655, -0.03444890305399895, -0.026937730610370636, -0.37139859795570374, 0.051738038659095764, -0.07622560858726501, 0.3888537585735321, 0.1745041459798813, 0.24875789880752563, 0.10637012869119644, 0.1731060892343521, 0.13706398010253906, -0.24836598336696625, 0.22853896021842957, 0.015214282087981701, 0.22568319737911224, -0.13684438169002533, 0.1493281126022339, 0.11347971856594086, 0.10884922742843628, 0.07756499946117401, 0.1673472672700882, 0.2292352318763733, -0.06424033641815186, 0.15198968350887299, 0.06430451571941376, -0.16298708319664001, -0.11653156578540802, 0.17537352442741394, -0.07836229354143143, -0.049402859061956406, 0.13342104852199554, -0.3034736216068268, 0.10309641808271408, 0.05733418092131615, -0.3015175759792328, 0.0699855163693428, 0.1319712996482849, -0.06809830665588379, 0.192268505692482, -0.28694698214530945, 0.15630465745925903, 0.16836528480052948, 0.24121561646461487, 0.1482047438621521, -0.07740980386734009, -0.05400901287794113, 0.022007020190358162, -0.0667729526758194, -0.1432863026857376, -0.12609949707984924, -0.01456206850707531, -8.948249816894531, 0.015206562355160713, -0.10259649157524109, -0.1659073531627655, -0.16621316969394684, 0.09180592745542526, -0.15609343349933624, -0.10452989488840103, 0.04674280062317848, -0.005707238335162401, 0.27608951926231384, -0.02000902220606804, -0.16601012647151947, -0.00476900115609169, 0.2309069037437439, 0.2095881998538971]</t>
+          <t>['medium', 'high', 'high', 'high', 'high', 'low']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.0, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 5, 4, 1]</t>
+          <t>[30.0, 30.0, 40.0, 30.0, 35.0, 30.0]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'woman', 'man', 'man', 'woman', 'man']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 40.0, 30.0, 35.0, 30.0]</t>
+          <t>[1, 1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>['man', 'woman', 'man', 'man', 'woman', 'man']</t>
+          <t>[3, 3, 5, 4, 3, 5]</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2, 1]</t>
+          <t>[5, 1, 5, 3, 4, 5]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 4, 3, 5]</t>
+          <t>[5, 5, 5, 4, 4, 3]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[5, 1, 5, 3, 4, 5]</t>
+          <t>[1, 2, 1, 3, 2, 1]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 4, 4, 3]</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>[1, 2, 1, 3, 2, 1]</t>
-        </is>
+          <t>[1, 1, 1, 3, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1, 1]</t>
+          <t>[4, 1, 4, 3, 2, 2]</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[4, 1, 4, 3, 2, 2]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
           <t>[0.16666667 0.33333333 0.16666667 0.33333333 0.        ]</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="S5" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -933,85 +900,78 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 2, 3, 3]</t>
+          <t>[nan, 'none', '{}', '{}', '{}', 'bisexual']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[nan, 'none', '{}', '{}', '{}', 'bisexual']</t>
+          <t>['left', 'center', 'right', 'right', 'left', 'left']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[-0.011250785551965237, 0.03692465275526047, 0.1661459356546402, -0.41660019755363464, -0.5502957105636597, -0.2436494380235672, 0.37676510214805603, 0.4401107430458069, -0.04293752461671829, -0.10692060738801956, 0.18557336926460266, 0.22848467528820038, 0.18222923576831818, 0.4904644787311554, 0.08271650224924088, 0.19150088727474213, -0.4971628785133362, 0.1977461278438568, 0.3189277648925781, 0.02717539481818676, 0.31802898645401, -0.2099015861749649, 0.13104736804962158, 0.07412887364625931, 0.3909315764904022, 0.07909190654754639, -0.2744261920452118, -0.09733060002326965, -0.3621859848499298, 0.4643607437610626, -0.15381358563899994, 0.3069019913673401, -0.3901776969432831, 0.02036028727889061, -0.004675783682614565, -0.03024875745177269, 0.5459372997283936, 0.21485725045204163, 0.35100799798965454, -0.41015347838401794, -0.17163978517055511, -0.04134145751595497, -0.14092597365379333, 0.07557512074708939, -0.058584731072187424, -0.06752583384513855, -3.217146635055542, -0.1951458752155304, -0.4550357162952423, -0.7132078409194946, 0.22715187072753906, -0.13832753896713257, -0.022471515461802483, 0.39575591683387756, -0.027866508811712265, 0.2633087933063507, -0.041436970233917236, -0.1711496263742447, 0.2906907796859741, 0.14393015205860138, 0.24906179308891296, 0.1998407244682312, 0.1301438957452774, 0.5281883478164673, 0.02942855842411518, 0.20391574501991272, 0.12955765426158905, 0.14412975311279297, -0.12832650542259216, 0.6191879510879517, -0.3161623775959015, -0.11074928939342499, 0.25181958079338074, 0.1185368075966835, 0.2280731201171875, -0.5662438273429871, 0.3722200095653534, 0.14350935816764832, -0.21293596923351288, 0.2334587126970291, -0.018920352682471275, 0.0428706631064415, 0.027928771451115608, 0.2846980690956116, -0.3592093884944916, 0.637191653251648, -0.5845813751220703, -0.6571007966995239, 0.14740577340126038, 0.46827760338783264, -0.11866876482963562, -0.06089169159531593, -0.21997712552547455, -0.02039172500371933, 0.4750748872756958, 0.2533966302871704, 0.09502163529396057, 0.008615775965154171, -0.022822562605142593, 0.3571426570415497, 0.2987498342990875, -0.08675261586904526, 0.25950512290000916, -0.2075827717781067, -0.462153822183609, -0.11109206080436707, 0.2422436773777008, -0.5203351378440857, 0.2879084646701813, -2.3244428634643555, 0.36977335810661316, 0.0013492410071194172, -0.024480387568473816, -0.16821147501468658, -0.06831248104572296, 0.11237840354442596, 0.18135657906532288, 0.10593871027231216, 0.24141180515289307, 0.17574967443943024, -0.5493825674057007, 0.6790623664855957, -0.027905233204364777, 0.2520408630371094, 0.33044344186782837, 0.011952864937484264, 0.12195754796266556, 0.2219381481409073, 0.08734002709388733, 0.14882785081863403, 0.6750224232673645, 0.6087828278541565, -0.27186018228530884, -0.28780627250671387, -0.18098527193069458, -0.07680697739124298, 0.33889180421829224, -0.07985042780637741, -0.15879730880260468, -0.2679913341999054, -0.3289183974266052, -0.18060345947742462, -2.7765555381774902, 0.4164063632488251, -0.08964620530605316, -0.05993189662694931, -0.2858746647834778, -0.5774605870246887, -0.2542528212070465, 0.09346146136522293, -0.033496271818876266, -0.10492343455553055, 0.08208106458187103, 0.14147743582725525, -0.16354449093341827, 0.11544545739889145, -0.31463494896888733, -0.21775692701339722, -0.12494047731161118, 0.6251411437988281, 0.08800908923149109, -0.1527756154537201, 0.268637090921402, -0.011179798282682896, 0.13131996989250183, -0.08353244513273239, 0.1523822546005249, 0.24410571157932281, 0.00614604027941823, -0.27081769704818726, 0.1067504808306694, 0.2382662296295166, 0.6663962602615356, -0.007857969030737877, -0.12509611248970032, -0.5789480805397034, 0.15588319301605225, 0.4841007590293884, -0.13245625793933868, -0.04513494670391083, -0.5768578052520752, -0.0009823176078498363, 0.2097877413034439, 0.30707865953445435, 0.2964790165424347, -0.08654327690601349, 0.5796999931335449, -0.17642299830913544, 0.1306939423084259, 0.46691328287124634, -0.18135474622249603, 0.04602019116282463, 0.20522639155387878, 0.10927754640579224, 0.6772686839103699, -0.05303220823407173, 0.4397745132446289, -0.6090259552001953, -0.0940798968076706, 0.1897238790988922, 0.11157308518886566, -0.10486142337322235, 0.2086484581232071, -0.041755471378564835, -0.37250736355781555, 4.301802158355713, -0.20234046876430511, 0.32165348529815674, 0.2887864112854004, 0.20939046144485474, -0.20643384754657745, 0.4945608377456665, -0.3230874538421631, -0.4096989333629608, -0.07790470123291016, -0.04276196286082268, 0.3581642806529999, -0.11968906968832016, 0.03867419809103012, 0.010146686807274818, 0.0861659124493599, 0.0982419028878212, 0.03734210133552551, 0.24519385397434235, -0.15001708269119263, -0.3728387951850891, -0.048902805894613266, 0.2611406743526459, 0.009742874652147293, -1.6987429857254028, 0.06265676766633987, -0.16142985224723816, -0.014916334301233292, 0.3750181794166565, -0.047750916332006454, -0.09186357259750366, 0.29276394844055176, -0.16178090870380402, 0.3182034492492676, 0.21555423736572266, 0.07276859879493713, 0.5229365825653076, 0.20592354238033295, 0.28507569432258606, -0.14448048174381256, 0.9358420372009277, 0.35150426626205444, -0.09221045672893524, 0.20437105000019073, -0.1980961114168167, 0.4907777011394501, 0.14208075404167175, 0.2851746678352356, -0.41068020462989807, -0.009029832668602467, 0.1541065126657486, -0.21207717061042786, -0.09005147218704224, -0.2234725058078766, -0.6147305369377136, 0.19765296578407288, 0.037628065794706345, -0.4167049825191498, 0.17287175357341766, -0.6005526185035706, -0.2238117903470993, -0.14564649760723114, -0.07519669830799103, 0.09668606519699097, 0.013579356484115124, 0.5156649947166443, 0.10072681307792664, -0.4228370487689972, -3.194260835647583, -0.1128290444612503, 0.14976046979427338, 0.062345828860998154, 0.11016710102558136, -0.26421040296554565, -0.17983373999595642, -0.03297600522637367, -0.039089385420084, -0.5336459875106812, 0.17953349649906158, -0.44802308082580566, 0.3727813959121704, 0.15464156866073608, -0.1415794938802719, 0.40862035751342773, -0.3055618405342102, 0.3567133843898773, -0.2574083209037781, -0.2348620742559433, 0.2693527936935425, 0.6632035970687866, -0.1569608896970749, 0.1926054060459137, 0.02682369016110897, -0.04322749376296997, -0.09181453287601471, -0.08117219805717468, 0.47296229004859924, 0.2230982929468155, -0.03684508800506592, 0.07657842338085175, -0.2666175365447998, -0.16010038554668427, -0.3169019818305969, -3.912407875061035, -0.2209557443857193, -0.5411125421524048, -0.23865002393722534, 0.3733096420764923, -0.32979705929756165, 0.31547367572784424, -0.19462381303310394, -0.4836137294769287, -0.2190893441438675, 0.3204430639743805, 0.01817338354885578, 0.21354036033153534, -0.4255915880203247, 0.7301662564277649, 0.005153159610927105, 0.24443204700946808, -0.00266997329890728, 0.26940467953681946, 0.12786583602428436, 0.04508524760603905, 0.7617071270942688, -0.1608339250087738, 0.25583416223526, 0.3662710189819336, 0.42347365617752075, -0.30067840218544006, -0.4589698314666748, -0.13565151393413544, 0.05551352724432945, 0.07744916528463364, 0.09426257759332657, -0.059447724372148514, -0.2092411071062088, 0.06753036379814148, -0.4298533797264099, 0.13893257081508636, -0.09793455898761749, 0.3861079812049866, -0.07086262106895447, -0.13814744353294373, -0.1588127464056015, 0.18880461156368256, 0.13516144454479218, 0.0758424922823906, -0.1437738984823227, -0.022349491715431213, 0.004599534906446934, -0.4242320656776428, 0.5787267088890076, -0.11578278988599777, -0.15982258319854736, 1.1417268514633179, -0.2864741086959839, 0.2213871330022812, -0.18267115950584412, 0.04700462147593498, 0.4264342486858368, 0.04230194538831711, 0.03674978390336037, 0.6055810451507568, -0.22289779782295227, 0.02903022989630699, -0.8363138437271118, -0.17217926681041718, -0.06988594681024551, 0.3043361306190491, -0.4506310522556305, 0.16955707967281342, -0.16090454161167145, -0.05957946926355362, -0.1394965946674347, -0.43835514783859253, -1.369568109512329, 0.022245585918426514, 0.5549625754356384, -0.0725371390581131, 0.45700958371162415, 0.12479683756828308, -0.034087926149368286, 0.13221555948257446, 0.09472817927598953, 0.05995374545454979, 0.29000726342201233, -0.5039213299751282, -0.11943572014570236, -0.2925567924976349, -0.3630773723125458, -0.05867834761738777, 0.14939212799072266, -0.20873768627643585, 0.5671722888946533, 0.0022483025677502155, 0.15372471511363983, 0.28915899991989136, 0.169602632522583, -0.19654580950737, -1.0335997343063354, 0.13508281111717224, -0.24121174216270447, 0.16774719953536987, 0.25913456082344055, -0.4515891969203949, -0.0910244956612587, 0.1852220594882965, -0.2854662537574768, -0.13012392818927765, 0.3299283981323242, 0.3237608075141907, 0.38505834341049194, 0.08824338763952255, -0.4904473125934601, 0.005868338048458099, 0.3322685956954956, 0.365070104598999, -0.5786369442939758, 0.13984322547912598, 0.28733882308006287, -0.2143767923116684, 0.15688319504261017, 0.3469373285770416, -0.2056015133857727, -0.23609942197799683, -0.3597604036331177, -0.6419438719749451, 0.05705087259411812, 0.28771331906318665, -0.2633099853992462, -0.22238300740718842, -0.03557444363832474, -0.011355064809322357, -0.30754354596138, -0.7642691731452942, -0.7270411849021912, -0.4951423704624176, -0.3112557828426361, -0.02004021219909191, 0.11982171982526779, 0.4371989369392395, 0.08968735486268997, 0.4122485816478729, -0.14773739874362946, 0.10608993470668793, 0.07593121379613876, -0.21046361327171326, 0.4598639905452728, -0.3028618395328522, -0.026816722005605698, 0.13563427329063416, 0.645659863948822, -0.2966676652431488, -0.12031947821378708, -0.08636395633220673, -0.3562927842140198, 0.09101983904838562, 0.25827592611312866, -0.23704014718532562, 0.12622354924678802, -0.12407578527927399, -0.10018958151340485, 0.04457177221775055, -0.1347213238477707, -1.5122268199920654, 0.6988074779510498, 0.49914905428886414, 0.20140190422534943, 0.3622216582298279, -0.05582147091627121, -0.4259571433067322, 0.1136409267783165, -0.06062481552362442, -0.027277927845716476, -0.6243329644203186, -0.06753192096948624, -0.1764019876718521, 0.2701531648635864, 0.025271635502576828, 0.49203282594680786, 0.25583750009536743, -0.49550506472587585, 0.36754310131073, -0.09147431701421738, 0.18078427016735077, -0.12158340960741043, -0.00030068540945649147, -0.36478206515312195, -0.06896445900201797, -0.386116623878479, -0.06713919341564178, 0.8109493255615234, 0.12738479673862457, 0.3636704981327057, 0.11142310500144958, 0.1662352830171585, -0.5574994683265686, -0.0547952838242054, 0.1615518480539322, 0.12327054888010025, -0.030532067641615868, -0.5380824208259583, 0.8362537026405334, 0.2185857594013214, -0.4422597289085388, 0.10707098990678787, 0.19586791098117828, -0.09304016828536987, 0.425381064414978, 0.24792931973934174, 0.053487036377191544, 0.21868276596069336, 0.42360225319862366, -0.402201771736145, 0.03146269917488098, 0.1337844580411911, -0.2169223576784134, -0.34826070070266724, 0.11132674664258957, 0.14634746313095093, 0.0628833994269371, -0.197613924741745, -0.2991989254951477, -0.13653117418289185, -0.037683360278606415, -0.07115488499403, -0.5754272937774658, 0.22489430010318756, -0.3350019156932831, -0.7614160180091858, -0.11320824176073074, -0.49651414155960083, -0.6199592351913452, 0.1593654900789261, 0.3744382858276367, 0.11102049052715302, -0.19128313660621643, 0.6534485220909119, -0.08733829110860825, 0.6343050003051758, 0.09228003770112991, 0.13724564015865326, 0.25244981050491333, 0.4854782819747925, 0.3493744432926178, -0.3264426290988922, -0.05871807783842087, -0.01001640036702156, 0.30035027861595154, 0.36796706914901733, 0.006203248165547848, -0.03516464680433273, 0.4606335461139679, -0.2929368317127228, -0.46504709124565125, 0.15182101726531982, 0.011659864336252213, 0.2292252629995346, -0.4058360159397125, 0.2364157885313034, 0.42854028940200806, -0.13717235624790192, -0.0698370635509491, 0.07040055841207504, -0.5146098732948303, -0.06453893333673477, 0.21965204179286957, 0.09701350331306458, -0.26947861909866333, 0.04526422545313835, 0.2880892753601074, -0.24354957044124603, -0.26996952295303345, -0.3793756365776062, 0.6674094200134277, 0.20115242898464203, -0.093918576836586, -0.1424015909433365, -0.24509577453136444, -0.2279721051454544, 0.82595294713974, -0.23645339906215668, 1.9253125190734863, 0.04697822034358978, 0.04239703342318535, -0.3066582977771759, 0.38486483693122864, 0.31238725781440735, -0.22499613463878632, 0.2181573361158371, -0.4560790956020355, 0.6189208030700684, -0.4196920692920685, 0.2867099344730377, -0.7482959628105164, 0.08908218145370483, 0.46855831146240234, -0.15397566556930542, -0.1512833684682846, -0.3779965043067932, -0.46349358558654785, 0.2625357210636139, -0.34152713418006897, 0.2513485252857208, 0.40506142377853394, -0.13393351435661316, 0.386655330657959, 0.2673635482788086, 0.05729042366147041, 0.13005490601062775, 0.5417186617851257, 0.18275664746761322, -0.2976282238960266, 0.007183310575783253, 0.2816259562969208, -0.32847118377685547, -0.3246142864227295, 0.1808047890663147, 0.3919905722141266, -0.259752482175827, -0.03952068090438843, -0.07713379710912704, 0.10297472029924393, -0.05574323982000351, 0.7398309111595154, 0.041238006204366684, 0.19365294277668, 0.14993345737457275, -0.34095028042793274, -0.4567004144191742, 0.5509646534919739, 0.6606056094169617, 0.017770418897271156, 0.05884086713194847, -0.33150365948677063, 0.27543550729751587, 0.1082669049501419, 0.01819363795220852, -0.0617385096848011, -0.4492367208003998, 0.0034335844684392214, 0.4289334714412689, -0.3753639757633209, 0.2604338526725769, 0.17152516543865204, -0.2061876505613327, 0.08980212360620499, 0.1843584179878235, 0.08389323949813843, -0.09945549070835114, 0.29223471879959106, -0.1382196694612503, -0.3469184339046478, 0.4711081087589264, 0.23331521451473236, 0.13218314945697784, 0.26356515288352966, 0.14637500047683716, -0.0025473551359027624, -0.2971896231174469, -0.1401636004447937, -2.338118553161621, 0.6020610332489014, -0.1580846756696701, 0.17758478224277496, 0.009141512215137482, -0.07145022600889206, 0.24115866422653198, -0.17502012848854065, 0.13068051636219025, -0.1642814725637436, 0.27068978548049927, 0.45155131816864014, 0.18737179040908813, 0.15550555288791656, -0.046725206077098846, -0.6947062015533447, 0.024211494252085686, -0.5484278202056885, 0.18991228938102722, -0.3800763189792633, 0.17800070345401764, 0.05979204177856445, -0.049907200038433075, -0.12837399542331696, -0.3082817792892456, 0.5324125289916992, -0.545740008354187, -0.11611693352460861, 0.1341031938791275, -0.22901175916194916, 0.24185195565223694, 0.20402507483959198, -0.05294723063707352, -0.26942428946495056, 0.22652924060821533, 0.17342498898506165, -0.6534208059310913, 0.3017885386943817, 0.3580178916454315, 0.07719530910253525, 0.3686220943927765, 0.4505152404308319, 0.09699685871601105, 0.021500010043382645, 0.04782133549451828, -0.37843459844589233, 0.29375210404396057, -0.1283838450908661, 0.49929171800613403, 0.0754217803478241, 0.6392172574996948, 0.2897845506668091, 0.02087901346385479, 0.23647496104240417, 0.43292000889778137, 0.10079902410507202, -0.017304783686995506, 0.3222631812095642, 0.010324947535991669, -0.6439428925514221, -0.19991916418075562, 0.19414342939853668, -0.2796034812927246, -0.37465158104896545, 0.34436824917793274, 0.012202076613903046, 0.03536183387041092, -0.17769388854503632, 0.17942285537719727, -0.08643601834774017, -0.12166070938110352, 0.3037060797214508, 0.09528100490570068, -0.1902906894683838, -0.25699323415756226, -0.3341957628726959, 0.3172987103462219, 0.0024969938676804304, -0.17660778760910034, -0.0868145078420639, 0.09283584356307983, 0.37347882986068726, -0.41716983914375305, -0.34404411911964417, 0.27510499954223633, -6.11821985244751, -0.13460399210453033, 0.20534735918045044, -0.41917338967323303, -0.3865348696708679, -0.3942593038082123, -0.2669175863265991, -0.3192393481731415, 0.012009845115244389, -0.07991141080856323, 0.21990017592906952, 0.34874826669692993, -0.39007461071014404, -0.3816159665584564, 0.6081286072731018, 0.5463017821311951]</t>
+          <t>['medium', 'medium', 'high', 'high', 'medium', 'medium']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.5, 0.0, 0.5, 0.5, -0.5, -0.5]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 4, 3, 3]</t>
+          <t>[30.0, 30.0, 35.0, 35.0, 30.0, 40.0]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['man', 'man', 'man', 'woman', 'man', 'woman']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[30.0, 30.0, 35.0, 35.0, 30.0, 40.0]</t>
+          <t>[1, 3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>['man', 'man', 'man', 'woman', 'man', 'woman']</t>
+          <t>[3, 2, 5, 3, 5, 5]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>[2, 3, 5, 1, 2, 4]</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>[5, 5, 5, 5, 1, 5]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>[1, 3, 1, 1, 1, 1]</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>[3, 2, 5, 3, 5, 5]</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>[2, 3, 5, 1, 2, 4]</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 1, 5]</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>[1, 3, 1, 1, 1, 1]</t>
-        </is>
+          <t>[1, 1, 1, 1, 1, 1]</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1, 1]</t>
+          <t>[4, 3, 3, 1, 3, 1]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[4, 3, 3, 1, 3, 1]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
           <t>[0.33333333 0.         0.5        0.16666667 0.        ]</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="S6" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -1031,85 +991,78 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[4, 2, 4, 5, 5, 5]</t>
+          <t>['{}', '{}', '{}', 'None', 'immigrant', '{}']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['{}', '{}', '{}', 'None', 'immigrant', '{}']</t>
+          <t>['left', 'left', 'right', 'right', 'left', 'far left']</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[-0.19164827466011047, 0.24510705471038818, 0.07372259348630905, -0.20038162171840668, -0.4582807719707489, -0.408297061920166, 0.6677278876304626, 0.8496958613395691, 0.06635136902332306, -0.0910836011171341, 0.09753572940826416, -0.0895056426525116, -0.5154240727424622, 0.48673298954963684, 0.3210696280002594, 0.30378586053848267, -0.30976855754852295, 0.20589853823184967, 0.512686014175415, 0.16806423664093018, -0.1396131068468094, -0.3748125731945038, 0.18606840074062347, -0.26563000679016113, -0.10132645070552826, -0.20218290388584137, 0.14599157869815826, -0.04506443813443184, -0.05629532411694527, 0.12002607434988022, 0.01832800731062889, 0.2692866921424866, -0.2753032147884369, -0.2158203423023224, 0.3680790364742279, 0.23139068484306335, 0.4021678864955902, 0.022723982110619545, 0.2251298576593399, 0.338165819644928, -0.41460368037223816, -0.062170062214136124, -0.0020712357945740223, -0.03281715139746666, -0.039276473224163055, -0.5342500805854797, -2.97800350189209, -0.04374920204281807, 0.05129103362560272, -0.2438075840473175, 0.3796778619289398, -0.38566505908966064, -0.170058935880661, 0.3895868957042694, 0.23220416903495789, 0.40029218792915344, -0.3867444097995758, 0.0034269497264176607, 0.19734874367713928, 0.3645460605621338, 0.5193750262260437, 0.06999260187149048, -0.11555616557598114, -0.12672658264636993, 0.12462284415960312, -0.029693707823753357, -0.30668139457702637, 0.7084790468215942, -0.8602574467658997, 0.17334896326065063, -0.507513165473938, -0.136875182390213, 0.195960134267807, 0.0537654384970665, -0.01338244043290615, -0.29246413707733154, -0.06074024364352226, 0.2741246521472931, -0.5375352501869202, -0.009436435997486115, -0.19097617268562317, 0.4506327211856842, -0.10232196003198624, 0.008452984504401684, -0.19085398316383362, 0.7048638463020325, -0.25650015473365784, -0.16138510406017303, 0.12607578933238983, -0.08179298788309097, 0.2954972982406616, 0.14499814808368683, -0.20797894895076752, 0.10083570331335068, 0.4527116119861603, 0.08576269447803497, 0.19984081387519836, 0.22489379346370697, 0.19469290971755981, 0.29527491331100464, 0.525519847869873, 0.3212319314479828, 0.16017572581768036, -0.5874785780906677, 0.28380024433135986, -0.2477729320526123, 0.17378990352153778, -0.08910755813121796, 0.46266669034957886, -2.8064072132110596, 0.5216113924980164, 0.18998970091342926, -0.14160209894180298, -0.30620768666267395, -0.12218071520328522, 0.37652549147605896, 0.37594494223594666, -0.4659824073314667, 0.1406458616256714, 0.33486849069595337, -0.4454832375049591, 0.27796804904937744, -0.22072148323059082, 0.09391047805547714, 0.2760717570781708, 0.3961372375488281, 0.10438507050275803, 0.09217974543571472, 0.273657888174057, 0.6497241854667664, 0.08846826106309891, 0.37763890624046326, 0.05365518108010292, -0.47505131363868713, -0.32111749053001404, -0.0888824611902237, 0.40061813592910767, -0.2357919067144394, -0.1391202211380005, -0.028890460729599, -0.3930269479751587, -0.8217236995697021, -3.23081374168396, 0.2566516697406769, 0.3779686987400055, 0.27266228199005127, -0.5297287702560425, -0.118682861328125, 0.0383390448987484, 0.048139024525880814, -0.024661172181367874, -0.33573636412620544, 0.32887476682662964, 0.386528879404068, -0.2835957407951355, -0.05646994709968567, -0.036053113639354706, -0.21042266488075256, 0.008943824097514153, 0.6449427008628845, 0.3201097249984741, -0.04210750386118889, 0.020604455843567848, -0.019778577610850334, 0.08500909805297852, -0.26751911640167236, 0.014086440205574036, 0.5136634707450867, -0.20732738077640533, -0.15752685070037842, -0.3440001904964447, 0.3684103488922119, 0.8627016544342041, 0.052763763815164566, 0.1502290517091751, -0.4066465497016907, 0.23819780349731445, 0.22023515403270721, -0.08411471545696259, -0.14366258680820465, -0.3337234556674957, 0.136945903301239, 0.35408714413642883, 0.5513357520103455, 0.3885534107685089, -0.010680193081498146, 0.47991517186164856, 0.02768395096063614, -0.3532734215259552, 0.3423558473587036, -0.2917768657207489, -0.30890706181526184, 0.46552973985671997, 0.6151930689811707, 0.6338684558868408, -0.2022789716720581, -0.2972722053527832, -0.6612265110015869, 0.2694763243198395, 0.2668040990829468, 0.13317282497882843, -0.10078705102205276, -0.025287248194217682, 0.11496683955192566, -0.6205362677574158, 3.96030330657959, 0.2337723970413208, -0.17516091465950012, 0.5361489653587341, 0.5501111149787903, -0.07987645268440247, 0.11673307418823242, -0.46701478958129883, -0.17773136496543884, -0.35265257954597473, 0.13649435341358185, 0.3794156014919281, 0.22073988616466522, -0.19241516292095184, 0.24397531151771545, -0.005415416322648525, 0.2893853783607483, -0.18150418996810913, 0.39924466609954834, -0.030209872871637344, 0.17962084710597992, -0.257639080286026, 0.06461244821548462, 0.1263403743505478, -1.658042311668396, 0.19415497779846191, -0.13646726310253143, -0.25193843245506287, 0.17448240518569946, -0.25756433606147766, 0.4334106147289276, -0.06735260039567947, -0.3217914402484894, 0.08505436778068542, 0.10777640342712402, 0.1217767745256424, 0.5026577115058899, 0.1723981499671936, 0.056534454226493835, 0.060660529881715775, 0.35113587975502014, -0.0018667071126401424, -0.6985492706298828, 0.03644164651632309, 0.4569874107837677, 0.2708158493041992, -0.315421998500824, 0.03432556986808777, -0.6844878792762756, 0.06224264204502106, 0.16615641117095947, 0.13088847696781158, 0.33246058225631714, -0.5974152088165283, -0.3841339349746704, 0.03479566052556038, 0.02551409974694252, -0.12608638405799866, 0.3522259593009949, -0.40842363238334656, -0.39535725116729736, -0.38212358951568604, -0.04503502696752548, -0.39187800884246826, 0.014231951907277107, 0.2606249451637268, -0.19053766131401062, 0.04915407672524452, -3.4396400451660156, 0.4547640085220337, 0.2016143649816513, 0.09723825007677078, 0.37788400053977966, -0.21445274353027344, -0.14231088757514954, 0.103672094643116, 0.08816767483949661, -0.5292252898216248, 0.6366311311721802, 0.20433861017227173, -0.12620343267917633, 0.4847014546394348, 0.1634742021560669, 0.2611822783946991, 0.037551991641521454, 0.1564481407403946, -0.3110799193382263, 0.014466939494013786, 0.3516365587711334, 0.24826237559318542, -0.3114126920700073, 0.026865767315030098, 0.03104257769882679, 0.02548336610198021, -0.27552172541618347, -0.37645700573921204, 0.4864034056663513, -0.4843858778476715, 0.35214099287986755, 0.04512971639633179, -0.16359412670135498, -0.07790780812501907, -0.6437246799468994, -2.877007484436035, 0.2884202301502228, 0.00296395318582654, -0.44113409519195557, -0.08072967082262039, -0.1764223426580429, 0.5860447287559509, -0.4194130003452301, -0.6206190586090088, -0.21489456295967102, 0.3270544111728668, 0.13214263319969177, 0.09336012601852417, 0.00033401354448869824, 0.16899532079696655, 0.49334487318992615, 0.2814003527164459, -0.20098312199115753, 0.19879060983657837, -0.03244621679186821, 0.061018213629722595, 0.3014950454235077, -0.053576018661260605, 0.1248147115111351, 0.14030957221984863, -0.0386611670255661, -0.3928675055503845, -0.10276921838521957, 0.3525623083114624, 0.04176371544599533, 0.21291689574718475, 0.27892792224884033, 0.036369048058986664, -0.14963601529598236, -0.22574537992477417, -0.22393092513084412, 0.35870257019996643, 0.013616698794066906, 0.24648280441761017, -0.09049645066261292, 0.22166885435581207, 0.4827924370765686, -0.07554496824741364, 0.19156226515769958, 0.6840553879737854, -0.20460566878318787, -0.3661491274833679, -0.5311529636383057, -0.205900177359581, -0.08667854219675064, -0.11808137595653534, -0.3067430853843689, 0.7030326128005981, -0.1789092868566513, -0.23675106465816498, -0.09648378938436508, 0.43211814761161804, 0.18869329988956451, 0.2765704095363617, -0.23885849118232727, 0.6935006976127625, -0.2730972170829773, 0.10939999669790268, -0.14568647742271423, 0.11637827754020691, -0.16243353486061096, 0.3593973219394684, -0.6317253708839417, 0.1518843173980713, 0.24908359348773956, -0.056000277400016785, 0.5505136251449585, -0.2620927095413208, -1.0807931423187256, -0.20979411900043488, 0.2712096869945526, -0.24283914268016815, 0.1429419368505478, -0.06178032234311104, 0.11952506750822067, 0.1052401140332222, 0.10971241444349289, 0.0007157486979849637, 0.3128108084201813, -0.5446073412895203, 0.002652029739692807, 0.054550424218177795, 0.3232300281524658, -0.8282983303070068, -0.013339545577764511, -0.2313816398382187, 0.26026010513305664, -0.16922634840011597, 0.1945015788078308, -0.12262384593486786, 0.27016308903694153, 0.5596623420715332, -0.5935025215148926, 0.19407351315021515, -0.3867284953594208, 0.18819886445999146, -0.23583759367465973, 0.14081569015979767, -0.3173152506351471, 0.04267165809869766, -0.01801098883152008, -0.22143951058387756, 0.6399174928665161, -0.5076821446418762, 0.2938845157623291, -0.1504426747560501, 0.059579987078905106, 0.1349419802427292, 0.6918326020240784, 0.44226399064064026, -0.27654755115509033, -0.31416380405426025, 0.6921458840370178, 0.34632331132888794, -0.041358280926942825, 0.31910157203674316, 0.13670523464679718, -0.04609650745987892, -0.26573842763900757, -0.46046197414398193, -0.17474311590194702, -0.010774786584079266, 0.21124546229839325, -0.2506549656391144, 0.05266217514872551, 0.26425328850746155, -0.09295502305030823, -0.34485167264938354, -0.57659912109375, -0.002637488767504692, -0.30858248472213745, -0.19747228920459747, 0.005446853581815958, 0.5021294951438904, -0.17439152300357819, 0.1913726031780243, -0.22889888286590576, -0.2599051296710968, 0.545295238494873, -0.5809483528137207, 0.9059168696403503, -0.16381891071796417, -0.08430704474449158, -0.29159361124038696, 0.26130563020706177, -0.453090637922287, -0.5860328674316406, -0.18445229530334473, -0.7905458807945251, 0.5145899057388306, 0.30674776434898376, -0.15665078163146973, -0.010274163447320461, -0.2826630771160126, -0.17753750085830688, 0.08746267855167389, 0.4176737666130066, -1.6535612344741821, 0.20465010404586792, 0.5176762342453003, -0.19286905229091644, 0.6551369428634644, -0.2550574541091919, -0.3057389557361603, 0.5545822381973267, -0.3434443771839142, 0.09070255607366562, -0.4838918447494507, -0.0054054781794548035, -0.3305385410785675, 0.2940455973148346, 0.08882751315832138, -0.04194898158311844, 0.1241106316447258, -0.3534480333328247, -0.3736811876296997, 0.30397486686706543, 0.004519172012805939, 0.2748650014400482, 0.17399586737155914, -0.09785371273756027, -0.1855577677488327, -0.2281871885061264, -0.21976259350776672, 0.7101989984512329, -0.4327967166900635, 0.27629390358924866, 0.1662922501564026, -0.1638050228357315, -0.4014763832092285, -0.09098920971155167, 0.49464520812034607, 0.43304771184921265, 0.32080918550491333, 0.06274984776973724, 0.8179517388343811, 0.5851423740386963, -0.226453959941864, 0.39161908626556396, -0.02347426861524582, 0.4228699207305908, 0.2722546458244324, 0.10526186227798462, -0.04303229972720146, 0.4490645229816437, 0.6480507254600525, -0.48197805881500244, -0.09460679441690445, 0.12205280363559723, -0.5069171786308289, -0.7493430972099304, 0.3993034362792969, -0.13829606771469116, -0.310914009809494, 0.3234768807888031, -0.3182300627231598, 0.09234993904829025, -0.2417997121810913, 0.1798134744167328, -0.638672411441803, -0.05771524831652641, -0.28006115555763245, -0.44104447960853577, 0.12093167752027512, 0.0769425481557846, -0.010583163239061832, 0.6732715964317322, 0.5427714586257935, 0.5353928804397583, -0.6006384491920471, -0.22127994894981384, -0.12787437438964844, 0.3620242476463318, 0.06013040617108345, 0.11181006580591202, 0.27209627628326416, -0.20955464243888855, 0.34593018889427185, -0.807579755783081, -0.5775582194328308, 0.5409204363822937, -0.02873731218278408, 0.24082021415233612, -0.13981005549430847, -0.05797017738223076, 0.11740408837795258, 0.22988170385360718, -0.5531104207038879, -0.6847423315048218, 0.2649863660335541, 0.2672853469848633, 0.3451954126358032, -0.10093766450881958, 0.1745494306087494, -0.1915750950574875, 0.06951170414686203, -0.033979158848524094, -0.24006059765815735, 0.25452470779418945, 0.5313581228256226, -0.013443672098219395, 0.6373400688171387, 0.37523749470710754, 0.14931848645210266, 0.26657432317733765, -0.6284800171852112, -0.3389529287815094, 0.26048529148101807, 0.1442587524652481, -0.19539713859558105, -0.31131890416145325, 0.20769435167312622, -0.15146562457084656, 0.38622474670410156, -0.14692434668540955, 2.16040301322937, 0.2892966866493225, 0.16240957379341125, -0.39856451749801636, 0.5663319826126099, -0.09896737337112427, 0.1805577427148819, -0.08840185403823853, -0.2883470058441162, 0.21962928771972656, -0.09272915124893188, 0.2519668936729431, 4.958240970154293e-05, 0.23210066556930542, 0.5099530816078186, 0.5288278460502625, -0.14586661756038666, -0.4939904510974884, -0.42668256163597107, -0.04806998372077942, -0.3960345387458801, -0.06693911552429199, 0.33651864528656006, 0.0003529983514454216, -0.20948028564453125, 0.07369456440210342, 0.07899042963981628, -0.18911314010620117, 0.25403669476509094, 0.396759033203125, -0.7564601302146912, -0.035524725914001465, 0.5711250901222229, 0.5872853994369507, -0.24341456592082977, 0.07278706133365631, 0.232346311211586, -0.44576138257980347, 0.059212349355220795, -0.008786634542047977, -0.24360725283622742, -0.6272181272506714, 0.6675294637680054, 0.18302366137504578, 0.35254597663879395, 0.12698577344417572, -0.07981990277767181, -0.18744252622127533, 0.7362368702888489, -0.00964146014302969, -0.2995283901691437, -0.13315461575984955, -0.2723553478717804, 0.15739375352859497, 0.20337805151939392, 0.08520163595676422, -0.13200326263904572, -0.5903628468513489, -0.3395122289657593, 0.09871797263622284, -0.41703662276268005, 0.42235442996025085, 0.1742190569639206, -0.2577683627605438, -0.0725637823343277, 0.11506867408752441, -0.37862229347229004, 0.0073034199886024, 0.14432720839977264, -0.11842063814401627, 0.15290383994579315, 0.5317602157592773, -0.008331174962222576, 0.013400676660239697, 0.5127222537994385, 0.18407192826271057, 0.228047177195549, -0.28993460536003113, -0.2626085579395294, -3.236173152923584, 0.1706666499376297, 0.25422558188438416, -0.18305911123752594, -0.08924354612827301, 0.019216811284422874, 0.059890273958444595, -0.1317589432001114, 0.08469528704881668, -0.7019630670547485, 0.16164611279964447, 0.30405664443969727, -0.12850019335746765, -0.08189859241247177, 0.17561641335487366, -0.22100894153118134, 0.40156880021095276, -0.4562336802482605, -0.556627631187439, -0.33463501930236816, 0.030371762812137604, 0.3819870054721832, -0.23649631440639496, -0.23940223455429077, -0.1142936423420906, 0.03333212062716484, 0.5141474604606628, -0.3797993063926697, 0.06257864832878113, 0.04985616356134415, -0.09762069582939148, -0.030977386981248856, -0.012592471204698086, -0.1346411556005478, 0.20987637341022491, 0.01427067443728447, -0.545782744884491, -0.05716570466756821, 0.2080068290233612, -0.061954546719789505, 0.1259821653366089, 0.37951770424842834, -0.4688016176223755, -0.07125554233789444, -0.07596952468156815, -0.2462599277496338, 0.4076462686061859, -0.42994198203086853, 0.707909882068634, -0.061874035745859146, 0.28605416417121887, -0.07345134764909744, 0.1882917433977127, -0.15784277021884918, 0.18654629588127136, 0.29787424206733704, 0.4403696060180664, -0.0010919725755229592, 0.08094488084316254, -0.4952464997768402, 0.5117387175559998, -0.15489862859249115, -0.2530190944671631, -0.012920659966766834, 0.30635660886764526, -0.3816797137260437, 0.015753531828522682, 0.18933629989624023, 0.10030578821897507, -0.03963802009820938, -0.14209158718585968, 0.07355976104736328, 0.18117882311344147, 0.33587589859962463, 0.00099424016661942, -0.07707319408655167, 0.4239234924316406, 0.15456250309944153, 0.5243333578109741, -0.026983879506587982, -0.12279278039932251, -0.021700754761695862, -0.33382365107536316, 0.2140650898218155, 0.11083193123340607, -7.167384147644043, -0.38900530338287354, -0.05917663499712944, -0.17394766211509705, 0.3633168637752533, -0.49448254704475403, -0.13882599771022797, -0.5048572421073914, 0.14011603593826294, -0.08674301952123642, 0.3350716531276703, 0.2013920545578003, -0.3757869005203247, -0.7621421813964844, 0.5274125933647156, 0.22410990297794342]</t>
+          <t>['medium', 'medium', 'medium', 'high', 'high', 'high']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[-0.5, -0.5, 0.5, 0.5, -0.5, -1.0]</t>
+          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 4, 5, 4]</t>
+          <t>[35.0, 30.0, 35.0, 40.0, 40.0, 30.0]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['black', 'black', 'white', 'white', 'white', 'white']</t>
+          <t>['woman', 'woman', 'man', 'man', 'man', 'man']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[35.0, 30.0, 35.0, 40.0, 40.0, 30.0]</t>
+          <t>[1, 1, 1, 2, 5, 3]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>['woman', 'woman', 'man', 'man', 'man', 'man']</t>
+          <t>[4, 4, 4, 3, 5, 5]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 5, 3]</t>
+          <t>[3, 2, 5, 4, 5, 5]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 3, 5, 5]</t>
+          <t>[3, 5, 5, 4, 5, 4]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[3, 2, 5, 4, 5, 5]</t>
+          <t>[1, 1, 3, 2, 2, 1]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 4, 5, 4]</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>[1, 1, 3, 2, 2, 1]</t>
-        </is>
+          <t>[3, 1, 5, 4, 5, 5]</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[3, 1, 5, 4, 5, 5]</t>
+          <t>[3, 2, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[3, 2, 5, 5, 5, 5]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
           <t>[0.         0.16666667 0.16666667 0.         0.66666667]</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="S7" t="n">
         <v>0.25</v>
       </c>
     </row>
